--- a/school_2/floors/КП пол СОШ2.xlsx
+++ b/school_2/floors/КП пол СОШ2.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16056" windowHeight="8520"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16056" windowHeight="8520" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="9.7оргПлт" sheetId="25" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2748" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2754" uniqueCount="709">
   <si>
     <t>Номер п/п</t>
   </si>
@@ -2174,9 +2174,6 @@
     <t>Уборка мусора / ММП1, ММП2, обед-ый зал, подвал, спорт-зал 1, спорт-зал 2.</t>
   </si>
   <si>
-    <t>подвал 1, 2, 3 этаж.</t>
-  </si>
-  <si>
     <t>подв.</t>
   </si>
   <si>
@@ -2190,6 +2187,25 @@
     <t>1, 2, 3 этаж.
 Оргалит
 Защита плитки от покраски потолка</t>
+  </si>
+  <si>
+    <t>шт.</t>
+  </si>
+  <si>
+    <t>подвал 
+1, 2, 3 этаж.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 504 т.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 380 т.</t>
+  </si>
+  <si>
+    <t>Талоны / контейнер / 8 м3</t>
+  </si>
+  <si>
+    <t>Талоны / контейнер / 20 м3</t>
   </si>
 </sst>
 </file>
@@ -2759,7 +2775,7 @@
     <xf numFmtId="43" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="166">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3058,6 +3074,18 @@
     <xf numFmtId="165" fontId="28" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3076,12 +3104,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3091,14 +3113,20 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="28" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="28" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3183,6 +3211,12 @@
     </xf>
     <xf numFmtId="165" fontId="28" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4588,16 +4622,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="130" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
       <c r="I1" s="70"/>
       <c r="J1" s="70"/>
     </row>
@@ -4605,14 +4639,14 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="129"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="133"/>
       <c r="H2" s="122" t="s">
         <v>631</v>
       </c>
@@ -4627,16 +4661,16 @@
       <c r="A3" s="121">
         <v>1</v>
       </c>
-      <c r="B3" s="132" t="s">
+      <c r="B3" s="134" t="s">
         <v>645</v>
       </c>
-      <c r="C3" s="133"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="134"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="136"/>
       <c r="H3" s="123" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="I3" s="121" t="s">
         <v>20</v>
@@ -4668,13 +4702,13 @@
       <c r="C5" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="D5" s="124"/>
-      <c r="E5" s="124"/>
-      <c r="F5" s="124"/>
-      <c r="G5" s="124"/>
-      <c r="H5" s="124"/>
-      <c r="I5" s="124"/>
-      <c r="J5" s="124"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="128"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="128"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="128"/>
     </row>
     <row r="6" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="116">
@@ -4686,13 +4720,13 @@
       <c r="C6" s="116">
         <v>2996.1</v>
       </c>
-      <c r="D6" s="124"/>
-      <c r="E6" s="124"/>
-      <c r="F6" s="124"/>
-      <c r="G6" s="124"/>
-      <c r="H6" s="124"/>
-      <c r="I6" s="124"/>
-      <c r="J6" s="124"/>
+      <c r="D6" s="128"/>
+      <c r="E6" s="128"/>
+      <c r="F6" s="128"/>
+      <c r="G6" s="128"/>
+      <c r="H6" s="128"/>
+      <c r="I6" s="128"/>
+      <c r="J6" s="128"/>
     </row>
     <row r="7" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="117">
@@ -4704,13 +4738,13 @@
       <c r="C7" s="117">
         <v>165.4</v>
       </c>
-      <c r="D7" s="124"/>
-      <c r="E7" s="124"/>
-      <c r="F7" s="124"/>
-      <c r="G7" s="124"/>
-      <c r="H7" s="124"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="124"/>
+      <c r="D7" s="128"/>
+      <c r="E7" s="128"/>
+      <c r="F7" s="128"/>
+      <c r="G7" s="128"/>
+      <c r="H7" s="128"/>
+      <c r="I7" s="128"/>
+      <c r="J7" s="128"/>
     </row>
     <row r="8" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="116">
@@ -4722,30 +4756,30 @@
       <c r="C8" s="116">
         <v>212.9</v>
       </c>
-      <c r="D8" s="124"/>
-      <c r="E8" s="124"/>
-      <c r="F8" s="124"/>
-      <c r="G8" s="124"/>
-      <c r="H8" s="124"/>
-      <c r="I8" s="124"/>
-      <c r="J8" s="124"/>
+      <c r="D8" s="128"/>
+      <c r="E8" s="128"/>
+      <c r="F8" s="128"/>
+      <c r="G8" s="128"/>
+      <c r="H8" s="128"/>
+      <c r="I8" s="128"/>
+      <c r="J8" s="128"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="125" t="s">
+      <c r="A9" s="129" t="s">
         <v>630</v>
       </c>
-      <c r="B9" s="125"/>
+      <c r="B9" s="129"/>
       <c r="C9" s="118">
         <f>SUM(C6:C8)</f>
         <v>3374.4</v>
       </c>
-      <c r="D9" s="124"/>
-      <c r="E9" s="124"/>
-      <c r="F9" s="124"/>
-      <c r="G9" s="124"/>
-      <c r="H9" s="124"/>
-      <c r="I9" s="124"/>
-      <c r="J9" s="124"/>
+      <c r="D9" s="128"/>
+      <c r="E9" s="128"/>
+      <c r="F9" s="128"/>
+      <c r="G9" s="128"/>
+      <c r="H9" s="128"/>
+      <c r="I9" s="128"/>
+      <c r="J9" s="128"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -4780,17 +4814,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="130" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -4798,18 +4832,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="130" t="s">
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="131"/>
+      <c r="I2" s="139"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -4821,18 +4855,18 @@
       <c r="A3" s="89">
         <v>1</v>
       </c>
-      <c r="B3" s="132" t="s">
+      <c r="B3" s="134" t="s">
         <v>159</v>
       </c>
-      <c r="C3" s="133"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="135" t="s">
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="140" t="s">
         <v>636</v>
       </c>
-      <c r="I3" s="165"/>
+      <c r="I3" s="169"/>
       <c r="J3" s="89" t="s">
         <v>20</v>
       </c>
@@ -4845,18 +4879,18 @@
       <c r="A4" s="89">
         <v>2</v>
       </c>
-      <c r="B4" s="132" t="s">
+      <c r="B4" s="134" t="s">
         <v>175</v>
       </c>
-      <c r="C4" s="133"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="133"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="134"/>
-      <c r="H4" s="135" t="s">
+      <c r="C4" s="135"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="140" t="s">
         <v>623</v>
       </c>
-      <c r="I4" s="165"/>
+      <c r="I4" s="169"/>
       <c r="J4" s="89" t="s">
         <v>20</v>
       </c>
@@ -5305,17 +5339,17 @@
       <c r="K26" s="95"/>
     </row>
     <row r="28" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="126" t="s">
+      <c r="A28" s="130" t="s">
         <v>625</v>
       </c>
-      <c r="B28" s="126"/>
-      <c r="C28" s="126"/>
-      <c r="D28" s="126"/>
-      <c r="E28" s="126"/>
-      <c r="F28" s="126"/>
-      <c r="G28" s="126"/>
-      <c r="H28" s="126"/>
-      <c r="I28" s="126"/>
+      <c r="B28" s="130"/>
+      <c r="C28" s="130"/>
+      <c r="D28" s="130"/>
+      <c r="E28" s="130"/>
+      <c r="F28" s="130"/>
+      <c r="G28" s="130"/>
+      <c r="H28" s="130"/>
+      <c r="I28" s="130"/>
       <c r="J28" s="70"/>
       <c r="K28" s="70"/>
     </row>
@@ -5323,18 +5357,18 @@
       <c r="A29" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B29" s="127" t="s">
+      <c r="B29" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="128"/>
-      <c r="D29" s="128"/>
-      <c r="E29" s="128"/>
-      <c r="F29" s="128"/>
-      <c r="G29" s="129"/>
-      <c r="H29" s="130" t="s">
+      <c r="C29" s="132"/>
+      <c r="D29" s="132"/>
+      <c r="E29" s="132"/>
+      <c r="F29" s="132"/>
+      <c r="G29" s="133"/>
+      <c r="H29" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I29" s="131"/>
+      <c r="I29" s="139"/>
       <c r="J29" s="67" t="s">
         <v>5</v>
       </c>
@@ -5346,18 +5380,18 @@
       <c r="A30" s="89">
         <v>1</v>
       </c>
-      <c r="B30" s="132" t="s">
+      <c r="B30" s="134" t="s">
         <v>159</v>
       </c>
-      <c r="C30" s="133"/>
-      <c r="D30" s="133"/>
-      <c r="E30" s="133"/>
-      <c r="F30" s="133"/>
-      <c r="G30" s="134"/>
-      <c r="H30" s="135" t="s">
+      <c r="C30" s="135"/>
+      <c r="D30" s="135"/>
+      <c r="E30" s="135"/>
+      <c r="F30" s="135"/>
+      <c r="G30" s="136"/>
+      <c r="H30" s="140" t="s">
         <v>637</v>
       </c>
-      <c r="I30" s="165"/>
+      <c r="I30" s="169"/>
       <c r="J30" s="89" t="s">
         <v>20</v>
       </c>
@@ -5370,18 +5404,18 @@
       <c r="A31" s="89">
         <v>2</v>
       </c>
-      <c r="B31" s="132" t="s">
+      <c r="B31" s="134" t="s">
         <v>175</v>
       </c>
-      <c r="C31" s="133"/>
-      <c r="D31" s="133"/>
-      <c r="E31" s="133"/>
-      <c r="F31" s="133"/>
-      <c r="G31" s="134"/>
-      <c r="H31" s="135" t="s">
+      <c r="C31" s="135"/>
+      <c r="D31" s="135"/>
+      <c r="E31" s="135"/>
+      <c r="F31" s="135"/>
+      <c r="G31" s="136"/>
+      <c r="H31" s="140" t="s">
         <v>622</v>
       </c>
-      <c r="I31" s="165"/>
+      <c r="I31" s="169"/>
       <c r="J31" s="89" t="s">
         <v>20</v>
       </c>
@@ -10797,7 +10831,7 @@
       <c r="S148" s="10"/>
       <c r="T148" s="10"/>
     </row>
-    <row r="149" spans="1:20" ht="18" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:20" ht="36" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>239</v>
       </c>
@@ -12909,7 +12943,7 @@
       <c r="S210" s="10"/>
       <c r="T210" s="10"/>
     </row>
-    <row r="211" spans="1:20" ht="90" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:20" ht="72" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>353</v>
       </c>
@@ -19295,17 +19329,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="130" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -19313,18 +19347,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="130" t="s">
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="131"/>
+      <c r="I2" s="139"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -19336,18 +19370,18 @@
       <c r="A3" s="68">
         <v>1</v>
       </c>
-      <c r="B3" s="132" t="s">
+      <c r="B3" s="134" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="133"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="164" t="s">
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="168" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="163"/>
+      <c r="I3" s="167"/>
       <c r="J3" s="68" t="s">
         <v>20</v>
       </c>
@@ -19385,14 +19419,14 @@
       <c r="C5" s="64">
         <v>80.599999999999994</v>
       </c>
-      <c r="D5" s="156"/>
-      <c r="E5" s="156"/>
-      <c r="F5" s="156"/>
-      <c r="G5" s="156"/>
-      <c r="H5" s="156"/>
-      <c r="I5" s="156"/>
-      <c r="J5" s="156"/>
-      <c r="K5" s="156"/>
+      <c r="D5" s="160"/>
+      <c r="E5" s="160"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="160"/>
+      <c r="H5" s="160"/>
+      <c r="I5" s="160"/>
+      <c r="J5" s="160"/>
+      <c r="K5" s="160"/>
     </row>
     <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="54" t="s">
@@ -19404,14 +19438,14 @@
       <c r="C6" s="54">
         <v>64.8</v>
       </c>
-      <c r="D6" s="156"/>
-      <c r="E6" s="156"/>
-      <c r="F6" s="156"/>
-      <c r="G6" s="156"/>
-      <c r="H6" s="156"/>
-      <c r="I6" s="156"/>
-      <c r="J6" s="156"/>
-      <c r="K6" s="156"/>
+      <c r="D6" s="160"/>
+      <c r="E6" s="160"/>
+      <c r="F6" s="160"/>
+      <c r="G6" s="160"/>
+      <c r="H6" s="160"/>
+      <c r="I6" s="160"/>
+      <c r="J6" s="160"/>
+      <c r="K6" s="160"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="54" t="s">
@@ -19423,14 +19457,14 @@
       <c r="C7" s="54">
         <v>45.7</v>
       </c>
-      <c r="D7" s="156"/>
-      <c r="E7" s="156"/>
-      <c r="F7" s="156"/>
-      <c r="G7" s="156"/>
-      <c r="H7" s="156"/>
-      <c r="I7" s="156"/>
-      <c r="J7" s="156"/>
-      <c r="K7" s="156"/>
+      <c r="D7" s="160"/>
+      <c r="E7" s="160"/>
+      <c r="F7" s="160"/>
+      <c r="G7" s="160"/>
+      <c r="H7" s="160"/>
+      <c r="I7" s="160"/>
+      <c r="J7" s="160"/>
+      <c r="K7" s="160"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="64" t="s">
@@ -19442,14 +19476,14 @@
       <c r="C8" s="64">
         <v>18.899999999999999</v>
       </c>
-      <c r="D8" s="156"/>
-      <c r="E8" s="156"/>
-      <c r="F8" s="156"/>
-      <c r="G8" s="156"/>
-      <c r="H8" s="156"/>
-      <c r="I8" s="156"/>
-      <c r="J8" s="156"/>
-      <c r="K8" s="156"/>
+      <c r="D8" s="160"/>
+      <c r="E8" s="160"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="160"/>
+      <c r="H8" s="160"/>
+      <c r="I8" s="160"/>
+      <c r="J8" s="160"/>
+      <c r="K8" s="160"/>
     </row>
     <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="54" t="s">
@@ -19461,14 +19495,14 @@
       <c r="C9" s="54">
         <v>63.3</v>
       </c>
-      <c r="D9" s="156"/>
-      <c r="E9" s="156"/>
-      <c r="F9" s="156"/>
-      <c r="G9" s="156"/>
-      <c r="H9" s="156"/>
-      <c r="I9" s="156"/>
-      <c r="J9" s="156"/>
-      <c r="K9" s="156"/>
+      <c r="D9" s="160"/>
+      <c r="E9" s="160"/>
+      <c r="F9" s="160"/>
+      <c r="G9" s="160"/>
+      <c r="H9" s="160"/>
+      <c r="I9" s="160"/>
+      <c r="J9" s="160"/>
+      <c r="K9" s="160"/>
     </row>
     <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="64" t="s">
@@ -19480,14 +19514,14 @@
       <c r="C10" s="64">
         <v>64.3</v>
       </c>
-      <c r="D10" s="156"/>
-      <c r="E10" s="156"/>
-      <c r="F10" s="156"/>
-      <c r="G10" s="156"/>
-      <c r="H10" s="156"/>
-      <c r="I10" s="156"/>
-      <c r="J10" s="156"/>
-      <c r="K10" s="156"/>
+      <c r="D10" s="160"/>
+      <c r="E10" s="160"/>
+      <c r="F10" s="160"/>
+      <c r="G10" s="160"/>
+      <c r="H10" s="160"/>
+      <c r="I10" s="160"/>
+      <c r="J10" s="160"/>
+      <c r="K10" s="160"/>
     </row>
     <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="54" t="s">
@@ -19499,14 +19533,14 @@
       <c r="C11" s="54">
         <v>64.900000000000006</v>
       </c>
-      <c r="D11" s="156"/>
-      <c r="E11" s="156"/>
-      <c r="F11" s="156"/>
-      <c r="G11" s="156"/>
-      <c r="H11" s="156"/>
-      <c r="I11" s="156"/>
-      <c r="J11" s="156"/>
-      <c r="K11" s="156"/>
+      <c r="D11" s="160"/>
+      <c r="E11" s="160"/>
+      <c r="F11" s="160"/>
+      <c r="G11" s="160"/>
+      <c r="H11" s="160"/>
+      <c r="I11" s="160"/>
+      <c r="J11" s="160"/>
+      <c r="K11" s="160"/>
     </row>
     <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="64" t="s">
@@ -19518,14 +19552,14 @@
       <c r="C12" s="64">
         <v>63.5</v>
       </c>
-      <c r="D12" s="156"/>
-      <c r="E12" s="156"/>
-      <c r="F12" s="156"/>
-      <c r="G12" s="156"/>
-      <c r="H12" s="156"/>
-      <c r="I12" s="156"/>
-      <c r="J12" s="156"/>
-      <c r="K12" s="156"/>
+      <c r="D12" s="160"/>
+      <c r="E12" s="160"/>
+      <c r="F12" s="160"/>
+      <c r="G12" s="160"/>
+      <c r="H12" s="160"/>
+      <c r="I12" s="160"/>
+      <c r="J12" s="160"/>
+      <c r="K12" s="160"/>
     </row>
     <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="54" t="s">
@@ -19537,14 +19571,14 @@
       <c r="C13" s="54">
         <v>64</v>
       </c>
-      <c r="D13" s="156"/>
-      <c r="E13" s="156"/>
-      <c r="F13" s="156"/>
-      <c r="G13" s="156"/>
-      <c r="H13" s="156"/>
-      <c r="I13" s="156"/>
-      <c r="J13" s="156"/>
-      <c r="K13" s="156"/>
+      <c r="D13" s="160"/>
+      <c r="E13" s="160"/>
+      <c r="F13" s="160"/>
+      <c r="G13" s="160"/>
+      <c r="H13" s="160"/>
+      <c r="I13" s="160"/>
+      <c r="J13" s="160"/>
+      <c r="K13" s="160"/>
     </row>
     <row r="14" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="54" t="s">
@@ -19556,14 +19590,14 @@
       <c r="C14" s="54">
         <v>89</v>
       </c>
-      <c r="D14" s="156"/>
-      <c r="E14" s="156"/>
-      <c r="F14" s="156"/>
-      <c r="G14" s="156"/>
-      <c r="H14" s="156"/>
-      <c r="I14" s="156"/>
-      <c r="J14" s="156"/>
-      <c r="K14" s="156"/>
+      <c r="D14" s="160"/>
+      <c r="E14" s="160"/>
+      <c r="F14" s="160"/>
+      <c r="G14" s="160"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="160"/>
+      <c r="J14" s="160"/>
+      <c r="K14" s="160"/>
     </row>
     <row r="15" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="64" t="s">
@@ -19575,14 +19609,14 @@
       <c r="C15" s="64">
         <v>62.5</v>
       </c>
-      <c r="D15" s="156"/>
-      <c r="E15" s="156"/>
-      <c r="F15" s="156"/>
-      <c r="G15" s="156"/>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
-      <c r="J15" s="156"/>
-      <c r="K15" s="156"/>
+      <c r="D15" s="160"/>
+      <c r="E15" s="160"/>
+      <c r="F15" s="160"/>
+      <c r="G15" s="160"/>
+      <c r="H15" s="160"/>
+      <c r="I15" s="160"/>
+      <c r="J15" s="160"/>
+      <c r="K15" s="160"/>
     </row>
     <row r="16" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="54" t="s">
@@ -19594,14 +19628,14 @@
       <c r="C16" s="54">
         <v>64.5</v>
       </c>
-      <c r="D16" s="156"/>
-      <c r="E16" s="156"/>
-      <c r="F16" s="156"/>
-      <c r="G16" s="156"/>
-      <c r="H16" s="156"/>
-      <c r="I16" s="156"/>
-      <c r="J16" s="156"/>
-      <c r="K16" s="156"/>
+      <c r="D16" s="160"/>
+      <c r="E16" s="160"/>
+      <c r="F16" s="160"/>
+      <c r="G16" s="160"/>
+      <c r="H16" s="160"/>
+      <c r="I16" s="160"/>
+      <c r="J16" s="160"/>
+      <c r="K16" s="160"/>
     </row>
     <row r="17" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="64" t="s">
@@ -19613,14 +19647,14 @@
       <c r="C17" s="64">
         <v>64.2</v>
       </c>
-      <c r="D17" s="156"/>
-      <c r="E17" s="156"/>
-      <c r="F17" s="156"/>
-      <c r="G17" s="156"/>
-      <c r="H17" s="156"/>
-      <c r="I17" s="156"/>
-      <c r="J17" s="156"/>
-      <c r="K17" s="156"/>
+      <c r="D17" s="160"/>
+      <c r="E17" s="160"/>
+      <c r="F17" s="160"/>
+      <c r="G17" s="160"/>
+      <c r="H17" s="160"/>
+      <c r="I17" s="160"/>
+      <c r="J17" s="160"/>
+      <c r="K17" s="160"/>
     </row>
     <row r="18" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="51" t="s">
@@ -19630,14 +19664,14 @@
         <f>SUM(C5:C17)</f>
         <v>810.2</v>
       </c>
-      <c r="D18" s="156"/>
-      <c r="E18" s="156"/>
-      <c r="F18" s="156"/>
-      <c r="G18" s="156"/>
-      <c r="H18" s="156"/>
-      <c r="I18" s="156"/>
-      <c r="J18" s="156"/>
-      <c r="K18" s="156"/>
+      <c r="D18" s="160"/>
+      <c r="E18" s="160"/>
+      <c r="F18" s="160"/>
+      <c r="G18" s="160"/>
+      <c r="H18" s="160"/>
+      <c r="I18" s="160"/>
+      <c r="J18" s="160"/>
+      <c r="K18" s="160"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -19673,36 +19707,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="154" t="s">
+      <c r="A1" s="158" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="155"/>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
-      <c r="J1" s="155"/>
-      <c r="K1" s="155"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
     </row>
     <row r="2" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="130" t="s">
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="131"/>
+      <c r="I2" s="139"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -19714,18 +19748,18 @@
       <c r="A3" s="68">
         <v>1</v>
       </c>
-      <c r="B3" s="132" t="s">
+      <c r="B3" s="134" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="133"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="164" t="s">
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="163"/>
+      <c r="I3" s="167"/>
       <c r="J3" s="68" t="s">
         <v>20</v>
       </c>
@@ -19763,14 +19797,14 @@
       <c r="C5" s="76">
         <v>82.2</v>
       </c>
-      <c r="D5" s="156"/>
-      <c r="E5" s="156"/>
-      <c r="F5" s="156"/>
-      <c r="G5" s="156"/>
-      <c r="H5" s="156"/>
-      <c r="I5" s="156"/>
-      <c r="J5" s="156"/>
-      <c r="K5" s="156"/>
+      <c r="D5" s="160"/>
+      <c r="E5" s="160"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="160"/>
+      <c r="H5" s="160"/>
+      <c r="I5" s="160"/>
+      <c r="J5" s="160"/>
+      <c r="K5" s="160"/>
     </row>
     <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="77" t="s">
@@ -19782,14 +19816,14 @@
       <c r="C6" s="77">
         <v>63.6</v>
       </c>
-      <c r="D6" s="156"/>
-      <c r="E6" s="156"/>
-      <c r="F6" s="156"/>
-      <c r="G6" s="156"/>
-      <c r="H6" s="156"/>
-      <c r="I6" s="156"/>
-      <c r="J6" s="156"/>
-      <c r="K6" s="156"/>
+      <c r="D6" s="160"/>
+      <c r="E6" s="160"/>
+      <c r="F6" s="160"/>
+      <c r="G6" s="160"/>
+      <c r="H6" s="160"/>
+      <c r="I6" s="160"/>
+      <c r="J6" s="160"/>
+      <c r="K6" s="160"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="76" t="s">
@@ -19801,14 +19835,14 @@
       <c r="C7" s="76">
         <v>85.1</v>
       </c>
-      <c r="D7" s="156"/>
-      <c r="E7" s="156"/>
-      <c r="F7" s="156"/>
-      <c r="G7" s="156"/>
-      <c r="H7" s="156"/>
-      <c r="I7" s="156"/>
-      <c r="J7" s="156"/>
-      <c r="K7" s="156"/>
+      <c r="D7" s="160"/>
+      <c r="E7" s="160"/>
+      <c r="F7" s="160"/>
+      <c r="G7" s="160"/>
+      <c r="H7" s="160"/>
+      <c r="I7" s="160"/>
+      <c r="J7" s="160"/>
+      <c r="K7" s="160"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="77" t="s">
@@ -19820,14 +19854,14 @@
       <c r="C8" s="77">
         <v>103.5</v>
       </c>
-      <c r="D8" s="156"/>
-      <c r="E8" s="156"/>
-      <c r="F8" s="156"/>
-      <c r="G8" s="156"/>
-      <c r="H8" s="156"/>
-      <c r="I8" s="156"/>
-      <c r="J8" s="156"/>
-      <c r="K8" s="156"/>
+      <c r="D8" s="160"/>
+      <c r="E8" s="160"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="160"/>
+      <c r="H8" s="160"/>
+      <c r="I8" s="160"/>
+      <c r="J8" s="160"/>
+      <c r="K8" s="160"/>
     </row>
     <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="76" t="s">
@@ -19839,14 +19873,14 @@
       <c r="C9" s="76">
         <v>90.3</v>
       </c>
-      <c r="D9" s="156"/>
-      <c r="E9" s="156"/>
-      <c r="F9" s="156"/>
-      <c r="G9" s="156"/>
-      <c r="H9" s="156"/>
-      <c r="I9" s="156"/>
-      <c r="J9" s="156"/>
-      <c r="K9" s="156"/>
+      <c r="D9" s="160"/>
+      <c r="E9" s="160"/>
+      <c r="F9" s="160"/>
+      <c r="G9" s="160"/>
+      <c r="H9" s="160"/>
+      <c r="I9" s="160"/>
+      <c r="J9" s="160"/>
+      <c r="K9" s="160"/>
     </row>
     <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="76" t="s">
@@ -19858,14 +19892,14 @@
       <c r="C10" s="76">
         <v>63.3</v>
       </c>
-      <c r="D10" s="156"/>
-      <c r="E10" s="156"/>
-      <c r="F10" s="156"/>
-      <c r="G10" s="156"/>
-      <c r="H10" s="156"/>
-      <c r="I10" s="156"/>
-      <c r="J10" s="156"/>
-      <c r="K10" s="156"/>
+      <c r="D10" s="160"/>
+      <c r="E10" s="160"/>
+      <c r="F10" s="160"/>
+      <c r="G10" s="160"/>
+      <c r="H10" s="160"/>
+      <c r="I10" s="160"/>
+      <c r="J10" s="160"/>
+      <c r="K10" s="160"/>
     </row>
     <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="77" t="s">
@@ -19877,14 +19911,14 @@
       <c r="C11" s="77">
         <v>64</v>
       </c>
-      <c r="D11" s="156"/>
-      <c r="E11" s="156"/>
-      <c r="F11" s="156"/>
-      <c r="G11" s="156"/>
-      <c r="H11" s="156"/>
-      <c r="I11" s="156"/>
-      <c r="J11" s="156"/>
-      <c r="K11" s="156"/>
+      <c r="D11" s="160"/>
+      <c r="E11" s="160"/>
+      <c r="F11" s="160"/>
+      <c r="G11" s="160"/>
+      <c r="H11" s="160"/>
+      <c r="I11" s="160"/>
+      <c r="J11" s="160"/>
+      <c r="K11" s="160"/>
     </row>
     <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="76" t="s">
@@ -19896,14 +19930,14 @@
       <c r="C12" s="76">
         <v>90.9</v>
       </c>
-      <c r="D12" s="156"/>
-      <c r="E12" s="156"/>
-      <c r="F12" s="156"/>
-      <c r="G12" s="156"/>
-      <c r="H12" s="156"/>
-      <c r="I12" s="156"/>
-      <c r="J12" s="156"/>
-      <c r="K12" s="156"/>
+      <c r="D12" s="160"/>
+      <c r="E12" s="160"/>
+      <c r="F12" s="160"/>
+      <c r="G12" s="160"/>
+      <c r="H12" s="160"/>
+      <c r="I12" s="160"/>
+      <c r="J12" s="160"/>
+      <c r="K12" s="160"/>
     </row>
     <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="77" t="s">
@@ -19915,14 +19949,14 @@
       <c r="C13" s="77">
         <v>63.8</v>
       </c>
-      <c r="D13" s="156"/>
-      <c r="E13" s="156"/>
-      <c r="F13" s="156"/>
-      <c r="G13" s="156"/>
-      <c r="H13" s="156"/>
-      <c r="I13" s="156"/>
-      <c r="J13" s="156"/>
-      <c r="K13" s="156"/>
+      <c r="D13" s="160"/>
+      <c r="E13" s="160"/>
+      <c r="F13" s="160"/>
+      <c r="G13" s="160"/>
+      <c r="H13" s="160"/>
+      <c r="I13" s="160"/>
+      <c r="J13" s="160"/>
+      <c r="K13" s="160"/>
     </row>
     <row r="14" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="76" t="s">
@@ -19934,14 +19968,14 @@
       <c r="C14" s="76">
         <v>63.9</v>
       </c>
-      <c r="D14" s="156"/>
-      <c r="E14" s="156"/>
-      <c r="F14" s="156"/>
-      <c r="G14" s="156"/>
-      <c r="H14" s="156"/>
-      <c r="I14" s="156"/>
-      <c r="J14" s="156"/>
-      <c r="K14" s="156"/>
+      <c r="D14" s="160"/>
+      <c r="E14" s="160"/>
+      <c r="F14" s="160"/>
+      <c r="G14" s="160"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="160"/>
+      <c r="J14" s="160"/>
+      <c r="K14" s="160"/>
     </row>
     <row r="15" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="77" t="s">
@@ -19953,14 +19987,14 @@
       <c r="C15" s="77">
         <v>64.5</v>
       </c>
-      <c r="D15" s="156"/>
-      <c r="E15" s="156"/>
-      <c r="F15" s="156"/>
-      <c r="G15" s="156"/>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
-      <c r="J15" s="156"/>
-      <c r="K15" s="156"/>
+      <c r="D15" s="160"/>
+      <c r="E15" s="160"/>
+      <c r="F15" s="160"/>
+      <c r="G15" s="160"/>
+      <c r="H15" s="160"/>
+      <c r="I15" s="160"/>
+      <c r="J15" s="160"/>
+      <c r="K15" s="160"/>
     </row>
     <row r="16" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="76" t="s">
@@ -19972,14 +20006,14 @@
       <c r="C16" s="76">
         <v>64.400000000000006</v>
       </c>
-      <c r="D16" s="156"/>
-      <c r="E16" s="156"/>
-      <c r="F16" s="156"/>
-      <c r="G16" s="156"/>
-      <c r="H16" s="156"/>
-      <c r="I16" s="156"/>
-      <c r="J16" s="156"/>
-      <c r="K16" s="156"/>
+      <c r="D16" s="160"/>
+      <c r="E16" s="160"/>
+      <c r="F16" s="160"/>
+      <c r="G16" s="160"/>
+      <c r="H16" s="160"/>
+      <c r="I16" s="160"/>
+      <c r="J16" s="160"/>
+      <c r="K16" s="160"/>
     </row>
     <row r="17" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="75" t="s">
@@ -19989,14 +20023,14 @@
         <f>SUM(C5:C16)</f>
         <v>899.49999999999989</v>
       </c>
-      <c r="D17" s="156"/>
-      <c r="E17" s="156"/>
-      <c r="F17" s="156"/>
-      <c r="G17" s="156"/>
-      <c r="H17" s="156"/>
-      <c r="I17" s="156"/>
-      <c r="J17" s="156"/>
-      <c r="K17" s="156"/>
+      <c r="D17" s="160"/>
+      <c r="E17" s="160"/>
+      <c r="F17" s="160"/>
+      <c r="G17" s="160"/>
+      <c r="H17" s="160"/>
+      <c r="I17" s="160"/>
+      <c r="J17" s="160"/>
+      <c r="K17" s="160"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -20031,17 +20065,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="130" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -20049,18 +20083,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="130" t="s">
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="131"/>
+      <c r="I2" s="139"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -20072,18 +20106,18 @@
       <c r="A3" s="89">
         <v>1</v>
       </c>
-      <c r="B3" s="132" t="s">
+      <c r="B3" s="134" t="s">
         <v>413</v>
       </c>
-      <c r="C3" s="133"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="162" t="s">
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="166" t="s">
         <v>644</v>
       </c>
-      <c r="I3" s="163"/>
+      <c r="I3" s="167"/>
       <c r="J3" s="89" t="s">
         <v>20</v>
       </c>
@@ -20096,18 +20130,18 @@
       <c r="A4" s="89">
         <v>2</v>
       </c>
-      <c r="B4" s="132" t="s">
+      <c r="B4" s="134" t="s">
         <v>387</v>
       </c>
-      <c r="C4" s="133"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="133"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="134"/>
-      <c r="H4" s="162" t="s">
+      <c r="C4" s="135"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="166" t="s">
         <v>643</v>
       </c>
-      <c r="I4" s="163"/>
+      <c r="I4" s="167"/>
       <c r="J4" s="89" t="s">
         <v>20</v>
       </c>
@@ -20139,7 +20173,7 @@
       <c r="C6" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="D6" s="156"/>
+      <c r="D6" s="160"/>
       <c r="E6" s="69" t="s">
         <v>627</v>
       </c>
@@ -20149,10 +20183,10 @@
       <c r="G6" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="H6" s="124"/>
-      <c r="I6" s="124"/>
-      <c r="J6" s="124"/>
-      <c r="K6" s="124"/>
+      <c r="H6" s="128"/>
+      <c r="I6" s="128"/>
+      <c r="J6" s="128"/>
+      <c r="K6" s="128"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="54" t="s">
@@ -20164,7 +20198,7 @@
       <c r="C7" s="54">
         <v>10.5</v>
       </c>
-      <c r="D7" s="156"/>
+      <c r="D7" s="160"/>
       <c r="E7" s="64" t="s">
         <v>522</v>
       </c>
@@ -20174,10 +20208,10 @@
       <c r="G7" s="84">
         <v>4.8</v>
       </c>
-      <c r="H7" s="124"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="124"/>
-      <c r="K7" s="124"/>
+      <c r="H7" s="128"/>
+      <c r="I7" s="128"/>
+      <c r="J7" s="128"/>
+      <c r="K7" s="128"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="64" t="s">
@@ -20189,7 +20223,7 @@
       <c r="C8" s="64">
         <v>22.3</v>
       </c>
-      <c r="D8" s="156"/>
+      <c r="D8" s="160"/>
       <c r="E8" s="54" t="s">
         <v>532</v>
       </c>
@@ -20199,10 +20233,10 @@
       <c r="G8" s="83">
         <v>7.5</v>
       </c>
-      <c r="H8" s="124"/>
-      <c r="I8" s="124"/>
-      <c r="J8" s="124"/>
-      <c r="K8" s="124"/>
+      <c r="H8" s="128"/>
+      <c r="I8" s="128"/>
+      <c r="J8" s="128"/>
+      <c r="K8" s="128"/>
     </row>
     <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="54" t="s">
@@ -20214,7 +20248,7 @@
       <c r="C9" s="54">
         <v>19</v>
       </c>
-      <c r="D9" s="156"/>
+      <c r="D9" s="160"/>
       <c r="E9" s="54" t="s">
         <v>537</v>
       </c>
@@ -20224,10 +20258,10 @@
       <c r="G9" s="83">
         <v>4.5999999999999996</v>
       </c>
-      <c r="H9" s="124"/>
-      <c r="I9" s="124"/>
-      <c r="J9" s="124"/>
-      <c r="K9" s="124"/>
+      <c r="H9" s="128"/>
+      <c r="I9" s="128"/>
+      <c r="J9" s="128"/>
+      <c r="K9" s="128"/>
     </row>
     <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="54" t="s">
@@ -20239,7 +20273,7 @@
       <c r="C10" s="54">
         <v>10.1</v>
       </c>
-      <c r="D10" s="156"/>
+      <c r="D10" s="160"/>
       <c r="E10" s="81"/>
       <c r="F10" s="81" t="s">
         <v>630</v>
@@ -20248,10 +20282,10 @@
         <f>SUM(G7:G9)</f>
         <v>16.899999999999999</v>
       </c>
-      <c r="H10" s="124"/>
-      <c r="I10" s="124"/>
-      <c r="J10" s="124"/>
-      <c r="K10" s="124"/>
+      <c r="H10" s="128"/>
+      <c r="I10" s="128"/>
+      <c r="J10" s="128"/>
+      <c r="K10" s="128"/>
     </row>
     <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="64" t="s">
@@ -20263,14 +20297,14 @@
       <c r="C11" s="64">
         <v>5.6</v>
       </c>
-      <c r="D11" s="156"/>
-      <c r="E11" s="156"/>
-      <c r="F11" s="156"/>
-      <c r="G11" s="156"/>
-      <c r="H11" s="124"/>
-      <c r="I11" s="124"/>
-      <c r="J11" s="124"/>
-      <c r="K11" s="124"/>
+      <c r="D11" s="160"/>
+      <c r="E11" s="160"/>
+      <c r="F11" s="160"/>
+      <c r="G11" s="160"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="128"/>
+      <c r="J11" s="128"/>
+      <c r="K11" s="128"/>
     </row>
     <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="54" t="s">
@@ -20282,14 +20316,14 @@
       <c r="C12" s="54">
         <v>8.1999999999999993</v>
       </c>
-      <c r="D12" s="156"/>
-      <c r="E12" s="156"/>
-      <c r="F12" s="156"/>
-      <c r="G12" s="156"/>
-      <c r="H12" s="124"/>
-      <c r="I12" s="124"/>
-      <c r="J12" s="124"/>
-      <c r="K12" s="124"/>
+      <c r="D12" s="160"/>
+      <c r="E12" s="160"/>
+      <c r="F12" s="160"/>
+      <c r="G12" s="160"/>
+      <c r="H12" s="128"/>
+      <c r="I12" s="128"/>
+      <c r="J12" s="128"/>
+      <c r="K12" s="128"/>
     </row>
     <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="64" t="s">
@@ -20301,14 +20335,14 @@
       <c r="C13" s="64">
         <v>15.7</v>
       </c>
-      <c r="D13" s="156"/>
-      <c r="E13" s="156"/>
-      <c r="F13" s="156"/>
-      <c r="G13" s="156"/>
-      <c r="H13" s="124"/>
-      <c r="I13" s="124"/>
-      <c r="J13" s="124"/>
-      <c r="K13" s="124"/>
+      <c r="D13" s="160"/>
+      <c r="E13" s="160"/>
+      <c r="F13" s="160"/>
+      <c r="G13" s="160"/>
+      <c r="H13" s="128"/>
+      <c r="I13" s="128"/>
+      <c r="J13" s="128"/>
+      <c r="K13" s="128"/>
     </row>
     <row r="14" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="51" t="s">
@@ -20318,14 +20352,14 @@
         <f>SUM(C7:C13)</f>
         <v>91.4</v>
       </c>
-      <c r="D14" s="156"/>
-      <c r="E14" s="156"/>
-      <c r="F14" s="156"/>
-      <c r="G14" s="156"/>
-      <c r="H14" s="124"/>
-      <c r="I14" s="124"/>
-      <c r="J14" s="124"/>
-      <c r="K14" s="124"/>
+      <c r="D14" s="160"/>
+      <c r="E14" s="160"/>
+      <c r="F14" s="160"/>
+      <c r="G14" s="160"/>
+      <c r="H14" s="128"/>
+      <c r="I14" s="128"/>
+      <c r="J14" s="128"/>
+      <c r="K14" s="128"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -20365,17 +20399,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="130" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -20383,18 +20417,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="130" t="s">
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="131"/>
+      <c r="I2" s="139"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -20406,18 +20440,18 @@
       <c r="A3" s="79">
         <v>1</v>
       </c>
-      <c r="B3" s="132" t="s">
+      <c r="B3" s="134" t="s">
         <v>413</v>
       </c>
-      <c r="C3" s="133"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="162" t="s">
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="166" t="s">
         <v>632</v>
       </c>
-      <c r="I3" s="163"/>
+      <c r="I3" s="167"/>
       <c r="J3" s="79" t="s">
         <v>20</v>
       </c>
@@ -20430,18 +20464,18 @@
       <c r="A4" s="79">
         <v>2</v>
       </c>
-      <c r="B4" s="132" t="s">
+      <c r="B4" s="134" t="s">
         <v>387</v>
       </c>
-      <c r="C4" s="133"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="133"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="134"/>
-      <c r="H4" s="162" t="s">
+      <c r="C4" s="135"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="166" t="s">
         <v>633</v>
       </c>
-      <c r="I4" s="163"/>
+      <c r="I4" s="167"/>
       <c r="J4" s="79" t="s">
         <v>20</v>
       </c>
@@ -20473,7 +20507,7 @@
       <c r="C6" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="D6" s="156"/>
+      <c r="D6" s="160"/>
       <c r="E6" s="69" t="s">
         <v>627</v>
       </c>
@@ -20483,10 +20517,10 @@
       <c r="G6" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="H6" s="124"/>
-      <c r="I6" s="124"/>
-      <c r="J6" s="124"/>
-      <c r="K6" s="124"/>
+      <c r="H6" s="128"/>
+      <c r="I6" s="128"/>
+      <c r="J6" s="128"/>
+      <c r="K6" s="128"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="54" t="s">
@@ -20498,7 +20532,7 @@
       <c r="C7" s="54">
         <v>9.6</v>
       </c>
-      <c r="D7" s="156"/>
+      <c r="D7" s="160"/>
       <c r="E7" s="64" t="s">
         <v>540</v>
       </c>
@@ -20508,10 +20542,10 @@
       <c r="G7" s="84">
         <v>4.8</v>
       </c>
-      <c r="H7" s="124"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="124"/>
-      <c r="K7" s="124"/>
+      <c r="H7" s="128"/>
+      <c r="I7" s="128"/>
+      <c r="J7" s="128"/>
+      <c r="K7" s="128"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="64" t="s">
@@ -20523,7 +20557,7 @@
       <c r="C8" s="64">
         <v>21.9</v>
       </c>
-      <c r="D8" s="156"/>
+      <c r="D8" s="160"/>
       <c r="E8" s="54" t="s">
         <v>546</v>
       </c>
@@ -20533,10 +20567,10 @@
       <c r="G8" s="83">
         <v>7.5</v>
       </c>
-      <c r="H8" s="124"/>
-      <c r="I8" s="124"/>
-      <c r="J8" s="124"/>
-      <c r="K8" s="124"/>
+      <c r="H8" s="128"/>
+      <c r="I8" s="128"/>
+      <c r="J8" s="128"/>
+      <c r="K8" s="128"/>
     </row>
     <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="54" t="s">
@@ -20548,7 +20582,7 @@
       <c r="C9" s="54">
         <v>19.600000000000001</v>
       </c>
-      <c r="D9" s="156"/>
+      <c r="D9" s="160"/>
       <c r="E9" s="64" t="s">
         <v>547</v>
       </c>
@@ -20558,10 +20592,10 @@
       <c r="G9" s="84">
         <v>4.5</v>
       </c>
-      <c r="H9" s="124"/>
-      <c r="I9" s="124"/>
-      <c r="J9" s="124"/>
-      <c r="K9" s="124"/>
+      <c r="H9" s="128"/>
+      <c r="I9" s="128"/>
+      <c r="J9" s="128"/>
+      <c r="K9" s="128"/>
     </row>
     <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="54" t="s">
@@ -20573,7 +20607,7 @@
       <c r="C10" s="54">
         <v>10.5</v>
       </c>
-      <c r="D10" s="156"/>
+      <c r="D10" s="160"/>
       <c r="E10" s="81"/>
       <c r="F10" s="81" t="s">
         <v>630</v>
@@ -20582,10 +20616,10 @@
         <f>SUM(G7:G9)</f>
         <v>16.8</v>
       </c>
-      <c r="H10" s="124"/>
-      <c r="I10" s="124"/>
-      <c r="J10" s="124"/>
-      <c r="K10" s="124"/>
+      <c r="H10" s="128"/>
+      <c r="I10" s="128"/>
+      <c r="J10" s="128"/>
+      <c r="K10" s="128"/>
     </row>
     <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="64" t="s">
@@ -20597,14 +20631,14 @@
       <c r="C11" s="64">
         <v>5.6</v>
       </c>
-      <c r="D11" s="156"/>
-      <c r="E11" s="156"/>
-      <c r="F11" s="156"/>
-      <c r="G11" s="156"/>
-      <c r="H11" s="124"/>
-      <c r="I11" s="124"/>
-      <c r="J11" s="124"/>
-      <c r="K11" s="124"/>
+      <c r="D11" s="160"/>
+      <c r="E11" s="160"/>
+      <c r="F11" s="160"/>
+      <c r="G11" s="160"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="128"/>
+      <c r="J11" s="128"/>
+      <c r="K11" s="128"/>
     </row>
     <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="54" t="s">
@@ -20616,14 +20650,14 @@
       <c r="C12" s="54">
         <v>8.1999999999999993</v>
       </c>
-      <c r="D12" s="156"/>
-      <c r="E12" s="156"/>
-      <c r="F12" s="156"/>
-      <c r="G12" s="156"/>
-      <c r="H12" s="124"/>
-      <c r="I12" s="124"/>
-      <c r="J12" s="124"/>
-      <c r="K12" s="124"/>
+      <c r="D12" s="160"/>
+      <c r="E12" s="160"/>
+      <c r="F12" s="160"/>
+      <c r="G12" s="160"/>
+      <c r="H12" s="128"/>
+      <c r="I12" s="128"/>
+      <c r="J12" s="128"/>
+      <c r="K12" s="128"/>
     </row>
     <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="64" t="s">
@@ -20635,14 +20669,14 @@
       <c r="C13" s="64">
         <v>15.7</v>
       </c>
-      <c r="D13" s="156"/>
-      <c r="E13" s="156"/>
-      <c r="F13" s="156"/>
-      <c r="G13" s="156"/>
-      <c r="H13" s="124"/>
-      <c r="I13" s="124"/>
-      <c r="J13" s="124"/>
-      <c r="K13" s="124"/>
+      <c r="D13" s="160"/>
+      <c r="E13" s="160"/>
+      <c r="F13" s="160"/>
+      <c r="G13" s="160"/>
+      <c r="H13" s="128"/>
+      <c r="I13" s="128"/>
+      <c r="J13" s="128"/>
+      <c r="K13" s="128"/>
     </row>
     <row r="14" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="51" t="s">
@@ -20652,14 +20686,14 @@
         <f>SUM(C7:C13)</f>
         <v>91.100000000000009</v>
       </c>
-      <c r="D14" s="156"/>
-      <c r="E14" s="156"/>
-      <c r="F14" s="156"/>
-      <c r="G14" s="156"/>
-      <c r="H14" s="124"/>
-      <c r="I14" s="124"/>
-      <c r="J14" s="124"/>
-      <c r="K14" s="124"/>
+      <c r="D14" s="160"/>
+      <c r="E14" s="160"/>
+      <c r="F14" s="160"/>
+      <c r="G14" s="160"/>
+      <c r="H14" s="128"/>
+      <c r="I14" s="128"/>
+      <c r="J14" s="128"/>
+      <c r="K14" s="128"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -20699,17 +20733,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="130" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -20717,18 +20751,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="130" t="s">
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="131"/>
+      <c r="I2" s="139"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -20740,18 +20774,18 @@
       <c r="A3" s="79">
         <v>1</v>
       </c>
-      <c r="B3" s="132" t="s">
+      <c r="B3" s="134" t="s">
         <v>159</v>
       </c>
-      <c r="C3" s="133"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="135" t="s">
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="140" t="s">
         <v>636</v>
       </c>
-      <c r="I3" s="165"/>
+      <c r="I3" s="169"/>
       <c r="J3" s="79" t="s">
         <v>20</v>
       </c>
@@ -20789,14 +20823,14 @@
       <c r="C5" s="64">
         <v>23.5</v>
       </c>
-      <c r="D5" s="156"/>
-      <c r="E5" s="156"/>
-      <c r="F5" s="156"/>
-      <c r="G5" s="156"/>
-      <c r="H5" s="156"/>
-      <c r="I5" s="156"/>
-      <c r="J5" s="156"/>
-      <c r="K5" s="156"/>
+      <c r="D5" s="160"/>
+      <c r="E5" s="160"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="160"/>
+      <c r="H5" s="160"/>
+      <c r="I5" s="160"/>
+      <c r="J5" s="160"/>
+      <c r="K5" s="160"/>
     </row>
     <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="54" t="s">
@@ -20808,14 +20842,14 @@
       <c r="C6" s="54">
         <v>4.8</v>
       </c>
-      <c r="D6" s="156"/>
-      <c r="E6" s="156"/>
-      <c r="F6" s="156"/>
-      <c r="G6" s="156"/>
-      <c r="H6" s="156"/>
-      <c r="I6" s="156"/>
-      <c r="J6" s="156"/>
-      <c r="K6" s="156"/>
+      <c r="D6" s="160"/>
+      <c r="E6" s="160"/>
+      <c r="F6" s="160"/>
+      <c r="G6" s="160"/>
+      <c r="H6" s="160"/>
+      <c r="I6" s="160"/>
+      <c r="J6" s="160"/>
+      <c r="K6" s="160"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="64" t="s">
@@ -20827,14 +20861,14 @@
       <c r="C7" s="64">
         <v>19.5</v>
       </c>
-      <c r="D7" s="156"/>
-      <c r="E7" s="156"/>
-      <c r="F7" s="156"/>
-      <c r="G7" s="156"/>
-      <c r="H7" s="156"/>
-      <c r="I7" s="156"/>
-      <c r="J7" s="156"/>
-      <c r="K7" s="156"/>
+      <c r="D7" s="160"/>
+      <c r="E7" s="160"/>
+      <c r="F7" s="160"/>
+      <c r="G7" s="160"/>
+      <c r="H7" s="160"/>
+      <c r="I7" s="160"/>
+      <c r="J7" s="160"/>
+      <c r="K7" s="160"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="54" t="s">
@@ -20846,14 +20880,14 @@
       <c r="C8" s="54">
         <v>10.3</v>
       </c>
-      <c r="D8" s="156"/>
-      <c r="E8" s="156"/>
-      <c r="F8" s="156"/>
-      <c r="G8" s="156"/>
-      <c r="H8" s="156"/>
-      <c r="I8" s="156"/>
-      <c r="J8" s="156"/>
-      <c r="K8" s="156"/>
+      <c r="D8" s="160"/>
+      <c r="E8" s="160"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="160"/>
+      <c r="H8" s="160"/>
+      <c r="I8" s="160"/>
+      <c r="J8" s="160"/>
+      <c r="K8" s="160"/>
     </row>
     <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="64" t="s">
@@ -20865,14 +20899,14 @@
       <c r="C9" s="64">
         <v>5.6</v>
       </c>
-      <c r="D9" s="156"/>
-      <c r="E9" s="156"/>
-      <c r="F9" s="156"/>
-      <c r="G9" s="156"/>
-      <c r="H9" s="156"/>
-      <c r="I9" s="156"/>
-      <c r="J9" s="156"/>
-      <c r="K9" s="156"/>
+      <c r="D9" s="160"/>
+      <c r="E9" s="160"/>
+      <c r="F9" s="160"/>
+      <c r="G9" s="160"/>
+      <c r="H9" s="160"/>
+      <c r="I9" s="160"/>
+      <c r="J9" s="160"/>
+      <c r="K9" s="160"/>
     </row>
     <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="54" t="s">
@@ -20884,14 +20918,14 @@
       <c r="C10" s="54">
         <v>8.1999999999999993</v>
       </c>
-      <c r="D10" s="156"/>
-      <c r="E10" s="156"/>
-      <c r="F10" s="156"/>
-      <c r="G10" s="156"/>
-      <c r="H10" s="156"/>
-      <c r="I10" s="156"/>
-      <c r="J10" s="156"/>
-      <c r="K10" s="156"/>
+      <c r="D10" s="160"/>
+      <c r="E10" s="160"/>
+      <c r="F10" s="160"/>
+      <c r="G10" s="160"/>
+      <c r="H10" s="160"/>
+      <c r="I10" s="160"/>
+      <c r="J10" s="160"/>
+      <c r="K10" s="160"/>
     </row>
     <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="64" t="s">
@@ -20903,14 +20937,14 @@
       <c r="C11" s="64">
         <v>7.6</v>
       </c>
-      <c r="D11" s="156"/>
-      <c r="E11" s="156"/>
-      <c r="F11" s="156"/>
-      <c r="G11" s="156"/>
-      <c r="H11" s="156"/>
-      <c r="I11" s="156"/>
-      <c r="J11" s="156"/>
-      <c r="K11" s="156"/>
+      <c r="D11" s="160"/>
+      <c r="E11" s="160"/>
+      <c r="F11" s="160"/>
+      <c r="G11" s="160"/>
+      <c r="H11" s="160"/>
+      <c r="I11" s="160"/>
+      <c r="J11" s="160"/>
+      <c r="K11" s="160"/>
     </row>
     <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="64" t="s">
@@ -20922,14 +20956,14 @@
       <c r="C12" s="64">
         <v>4.7</v>
       </c>
-      <c r="D12" s="156"/>
-      <c r="E12" s="156"/>
-      <c r="F12" s="156"/>
-      <c r="G12" s="156"/>
-      <c r="H12" s="156"/>
-      <c r="I12" s="156"/>
-      <c r="J12" s="156"/>
-      <c r="K12" s="156"/>
+      <c r="D12" s="160"/>
+      <c r="E12" s="160"/>
+      <c r="F12" s="160"/>
+      <c r="G12" s="160"/>
+      <c r="H12" s="160"/>
+      <c r="I12" s="160"/>
+      <c r="J12" s="160"/>
+      <c r="K12" s="160"/>
     </row>
     <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="51" t="s">
@@ -20939,14 +20973,14 @@
         <f>SUM(C5:C12)</f>
         <v>84.199999999999989</v>
       </c>
-      <c r="D13" s="156"/>
-      <c r="E13" s="156"/>
-      <c r="F13" s="156"/>
-      <c r="G13" s="156"/>
-      <c r="H13" s="156"/>
-      <c r="I13" s="156"/>
-      <c r="J13" s="156"/>
-      <c r="K13" s="156"/>
+      <c r="D13" s="160"/>
+      <c r="E13" s="160"/>
+      <c r="F13" s="160"/>
+      <c r="G13" s="160"/>
+      <c r="H13" s="160"/>
+      <c r="I13" s="160"/>
+      <c r="J13" s="160"/>
+      <c r="K13" s="160"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -20964,7 +20998,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.21875" customWidth="1"/>
@@ -20973,191 +21007,243 @@
     <col min="4" max="4" width="4.109375" customWidth="1"/>
     <col min="5" max="5" width="7.109375" customWidth="1"/>
     <col min="6" max="7" width="3.21875" customWidth="1"/>
-    <col min="8" max="8" width="5.33203125" customWidth="1"/>
-    <col min="9" max="9" width="7.88671875" customWidth="1"/>
-    <col min="10" max="10" width="8.21875" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="130" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-    </row>
-    <row r="2" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+    </row>
+    <row r="2" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="130" t="s">
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="125" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="131"/>
-      <c r="J2" s="67" t="s">
+      <c r="I2" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="71" t="s">
+      <c r="J2" s="71" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="120">
         <v>1</v>
       </c>
-      <c r="B3" s="132" t="s">
+      <c r="B3" s="134" t="s">
         <v>698</v>
       </c>
-      <c r="C3" s="133"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="135" t="s">
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="126" t="s">
+        <v>704</v>
+      </c>
+      <c r="I3" s="120" t="s">
+        <v>700</v>
+      </c>
+      <c r="J3" s="127">
+        <f>C12</f>
+        <v>884</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="124">
+        <v>2</v>
+      </c>
+      <c r="B4" s="170" t="s">
+        <v>707</v>
+      </c>
+      <c r="C4" s="170"/>
+      <c r="D4" s="170"/>
+      <c r="E4" s="170"/>
+      <c r="F4" s="170"/>
+      <c r="G4" s="170"/>
+      <c r="H4" s="171" t="s">
+        <v>705</v>
+      </c>
+      <c r="I4" s="124" t="s">
+        <v>703</v>
+      </c>
+      <c r="J4" s="127">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="124">
+        <v>3</v>
+      </c>
+      <c r="B5" s="170" t="s">
+        <v>708</v>
+      </c>
+      <c r="C5" s="170"/>
+      <c r="D5" s="170"/>
+      <c r="E5" s="170"/>
+      <c r="F5" s="170"/>
+      <c r="G5" s="170"/>
+      <c r="H5" s="171" t="s">
+        <v>706</v>
+      </c>
+      <c r="I5" s="124" t="s">
+        <v>703</v>
+      </c>
+      <c r="J5" s="127">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="137"/>
+      <c r="B6" s="137"/>
+      <c r="C6" s="137"/>
+      <c r="D6" s="137"/>
+      <c r="E6" s="137"/>
+      <c r="F6" s="137"/>
+      <c r="G6" s="137"/>
+      <c r="H6" s="137"/>
+      <c r="I6" s="137"/>
+      <c r="J6" s="137"/>
+    </row>
+    <row r="7" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="69" t="s">
+        <v>647</v>
+      </c>
+      <c r="B7" s="69" t="s">
+        <v>696</v>
+      </c>
+      <c r="C7" s="69" t="s">
+        <v>701</v>
+      </c>
+      <c r="D7" s="128"/>
+      <c r="E7" s="128"/>
+      <c r="F7" s="128"/>
+      <c r="G7" s="128"/>
+      <c r="H7" s="128"/>
+      <c r="I7" s="128"/>
+      <c r="J7" s="128"/>
+    </row>
+    <row r="8" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="116">
+        <v>1</v>
+      </c>
+      <c r="B8" s="116" t="s">
         <v>699</v>
       </c>
-      <c r="I3" s="136"/>
-      <c r="J3" s="120" t="s">
-        <v>701</v>
-      </c>
-      <c r="K3" s="72">
-        <f>C9</f>
-        <v>205.6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="137"/>
-      <c r="B4" s="137"/>
-      <c r="C4" s="137"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137"/>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-    </row>
-    <row r="5" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="69" t="s">
-        <v>647</v>
-      </c>
-      <c r="B5" s="69" t="s">
-        <v>696</v>
-      </c>
-      <c r="C5" s="69" t="s">
-        <v>702</v>
-      </c>
-      <c r="D5" s="124"/>
-      <c r="E5" s="124"/>
-      <c r="F5" s="124"/>
-      <c r="G5" s="124"/>
-      <c r="H5" s="124"/>
-      <c r="I5" s="124"/>
-      <c r="J5" s="124"/>
-      <c r="K5" s="124"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="116">
+      <c r="C8" s="116">
+        <v>299</v>
+      </c>
+      <c r="D8" s="128"/>
+      <c r="E8" s="128"/>
+      <c r="F8" s="128"/>
+      <c r="G8" s="128"/>
+      <c r="H8" s="128"/>
+      <c r="I8" s="128"/>
+      <c r="J8" s="128"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="117">
+        <v>2</v>
+      </c>
+      <c r="B9" s="117">
         <v>1</v>
       </c>
-      <c r="B6" s="116" t="s">
-        <v>700</v>
-      </c>
-      <c r="C6" s="116">
-        <v>87.9</v>
-      </c>
-      <c r="D6" s="124"/>
-      <c r="E6" s="124"/>
-      <c r="F6" s="124"/>
-      <c r="G6" s="124"/>
-      <c r="H6" s="124"/>
-      <c r="I6" s="124"/>
-      <c r="J6" s="124"/>
-      <c r="K6" s="124"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="117">
+      <c r="C9" s="117">
+        <v>186</v>
+      </c>
+      <c r="D9" s="128"/>
+      <c r="E9" s="128"/>
+      <c r="F9" s="128"/>
+      <c r="G9" s="128"/>
+      <c r="H9" s="128"/>
+      <c r="I9" s="128"/>
+      <c r="J9" s="128"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="117">
+        <v>3</v>
+      </c>
+      <c r="B10" s="117">
         <v>2</v>
       </c>
-      <c r="B7" s="117">
-        <v>1</v>
-      </c>
-      <c r="C7" s="117">
-        <v>53.1</v>
-      </c>
-      <c r="D7" s="124"/>
-      <c r="E7" s="124"/>
-      <c r="F7" s="124"/>
-      <c r="G7" s="124"/>
-      <c r="H7" s="124"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="124"/>
-      <c r="K7" s="124"/>
-    </row>
-    <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="116">
+      <c r="C10" s="117">
+        <v>219</v>
+      </c>
+      <c r="D10" s="128"/>
+      <c r="E10" s="128"/>
+      <c r="F10" s="128"/>
+      <c r="G10" s="128"/>
+      <c r="H10" s="128"/>
+      <c r="I10" s="128"/>
+      <c r="J10" s="128"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="116">
+        <v>4</v>
+      </c>
+      <c r="B11" s="116">
         <v>3</v>
       </c>
-      <c r="B8" s="116">
-        <v>2</v>
-      </c>
-      <c r="C8" s="116">
-        <v>64.599999999999994</v>
-      </c>
-      <c r="D8" s="124"/>
-      <c r="E8" s="124"/>
-      <c r="F8" s="124"/>
-      <c r="G8" s="124"/>
-      <c r="H8" s="124"/>
-      <c r="I8" s="124"/>
-      <c r="J8" s="124"/>
-      <c r="K8" s="124"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="125" t="s">
+      <c r="C11" s="116">
+        <v>180</v>
+      </c>
+      <c r="D11" s="128"/>
+      <c r="E11" s="128"/>
+      <c r="F11" s="128"/>
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="128"/>
+      <c r="J11" s="128"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="129" t="s">
         <v>630</v>
       </c>
-      <c r="B9" s="125"/>
-      <c r="C9" s="118">
-        <f>SUM(C6:C8)</f>
-        <v>205.6</v>
-      </c>
-      <c r="D9" s="124"/>
-      <c r="E9" s="124"/>
-      <c r="F9" s="124"/>
-      <c r="G9" s="124"/>
-      <c r="H9" s="124"/>
-      <c r="I9" s="124"/>
-      <c r="J9" s="124"/>
-      <c r="K9" s="124"/>
+      <c r="B12" s="129"/>
+      <c r="C12" s="118">
+        <f>SUM(C8:C11)</f>
+        <v>884</v>
+      </c>
+      <c r="D12" s="128"/>
+      <c r="E12" s="128"/>
+      <c r="F12" s="128"/>
+      <c r="G12" s="128"/>
+      <c r="H12" s="128"/>
+      <c r="I12" s="128"/>
+      <c r="J12" s="128"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="D5:K9"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="D7:J12"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:I2"/>
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -21183,17 +21269,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="130" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -21201,18 +21287,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="130" t="s">
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="131"/>
+      <c r="I2" s="139"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -21224,18 +21310,18 @@
       <c r="A3" s="79">
         <v>1</v>
       </c>
-      <c r="B3" s="132" t="s">
+      <c r="B3" s="134" t="s">
         <v>159</v>
       </c>
-      <c r="C3" s="133"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="135" t="s">
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="140" t="s">
         <v>637</v>
       </c>
-      <c r="I3" s="165"/>
+      <c r="I3" s="169"/>
       <c r="J3" s="79" t="s">
         <v>20</v>
       </c>
@@ -21273,14 +21359,14 @@
       <c r="C5" s="64">
         <v>4.8</v>
       </c>
-      <c r="D5" s="156"/>
-      <c r="E5" s="156"/>
-      <c r="F5" s="156"/>
-      <c r="G5" s="156"/>
-      <c r="H5" s="156"/>
-      <c r="I5" s="156"/>
-      <c r="J5" s="156"/>
-      <c r="K5" s="156"/>
+      <c r="D5" s="160"/>
+      <c r="E5" s="160"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="160"/>
+      <c r="H5" s="160"/>
+      <c r="I5" s="160"/>
+      <c r="J5" s="160"/>
+      <c r="K5" s="160"/>
     </row>
     <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="54" t="s">
@@ -21292,14 +21378,14 @@
       <c r="C6" s="54">
         <v>23.6</v>
       </c>
-      <c r="D6" s="156"/>
-      <c r="E6" s="156"/>
-      <c r="F6" s="156"/>
-      <c r="G6" s="156"/>
-      <c r="H6" s="156"/>
-      <c r="I6" s="156"/>
-      <c r="J6" s="156"/>
-      <c r="K6" s="156"/>
+      <c r="D6" s="160"/>
+      <c r="E6" s="160"/>
+      <c r="F6" s="160"/>
+      <c r="G6" s="160"/>
+      <c r="H6" s="160"/>
+      <c r="I6" s="160"/>
+      <c r="J6" s="160"/>
+      <c r="K6" s="160"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="64" t="s">
@@ -21311,14 +21397,14 @@
       <c r="C7" s="64">
         <v>19.600000000000001</v>
       </c>
-      <c r="D7" s="156"/>
-      <c r="E7" s="156"/>
-      <c r="F7" s="156"/>
-      <c r="G7" s="156"/>
-      <c r="H7" s="156"/>
-      <c r="I7" s="156"/>
-      <c r="J7" s="156"/>
-      <c r="K7" s="156"/>
+      <c r="D7" s="160"/>
+      <c r="E7" s="160"/>
+      <c r="F7" s="160"/>
+      <c r="G7" s="160"/>
+      <c r="H7" s="160"/>
+      <c r="I7" s="160"/>
+      <c r="J7" s="160"/>
+      <c r="K7" s="160"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="54" t="s">
@@ -21330,14 +21416,14 @@
       <c r="C8" s="54">
         <v>10.5</v>
       </c>
-      <c r="D8" s="156"/>
-      <c r="E8" s="156"/>
-      <c r="F8" s="156"/>
-      <c r="G8" s="156"/>
-      <c r="H8" s="156"/>
-      <c r="I8" s="156"/>
-      <c r="J8" s="156"/>
-      <c r="K8" s="156"/>
+      <c r="D8" s="160"/>
+      <c r="E8" s="160"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="160"/>
+      <c r="H8" s="160"/>
+      <c r="I8" s="160"/>
+      <c r="J8" s="160"/>
+      <c r="K8" s="160"/>
     </row>
     <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="64" t="s">
@@ -21349,14 +21435,14 @@
       <c r="C9" s="64">
         <v>5.6</v>
       </c>
-      <c r="D9" s="156"/>
-      <c r="E9" s="156"/>
-      <c r="F9" s="156"/>
-      <c r="G9" s="156"/>
-      <c r="H9" s="156"/>
-      <c r="I9" s="156"/>
-      <c r="J9" s="156"/>
-      <c r="K9" s="156"/>
+      <c r="D9" s="160"/>
+      <c r="E9" s="160"/>
+      <c r="F9" s="160"/>
+      <c r="G9" s="160"/>
+      <c r="H9" s="160"/>
+      <c r="I9" s="160"/>
+      <c r="J9" s="160"/>
+      <c r="K9" s="160"/>
     </row>
     <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="54" t="s">
@@ -21368,14 +21454,14 @@
       <c r="C10" s="54">
         <v>8.1999999999999993</v>
       </c>
-      <c r="D10" s="156"/>
-      <c r="E10" s="156"/>
-      <c r="F10" s="156"/>
-      <c r="G10" s="156"/>
-      <c r="H10" s="156"/>
-      <c r="I10" s="156"/>
-      <c r="J10" s="156"/>
-      <c r="K10" s="156"/>
+      <c r="D10" s="160"/>
+      <c r="E10" s="160"/>
+      <c r="F10" s="160"/>
+      <c r="G10" s="160"/>
+      <c r="H10" s="160"/>
+      <c r="I10" s="160"/>
+      <c r="J10" s="160"/>
+      <c r="K10" s="160"/>
     </row>
     <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="64" t="s">
@@ -21387,14 +21473,14 @@
       <c r="C11" s="64">
         <v>7.6</v>
       </c>
-      <c r="D11" s="156"/>
-      <c r="E11" s="156"/>
-      <c r="F11" s="156"/>
-      <c r="G11" s="156"/>
-      <c r="H11" s="156"/>
-      <c r="I11" s="156"/>
-      <c r="J11" s="156"/>
-      <c r="K11" s="156"/>
+      <c r="D11" s="160"/>
+      <c r="E11" s="160"/>
+      <c r="F11" s="160"/>
+      <c r="G11" s="160"/>
+      <c r="H11" s="160"/>
+      <c r="I11" s="160"/>
+      <c r="J11" s="160"/>
+      <c r="K11" s="160"/>
     </row>
     <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="54" t="s">
@@ -21406,14 +21492,14 @@
       <c r="C12" s="54">
         <v>4.5</v>
       </c>
-      <c r="D12" s="156"/>
-      <c r="E12" s="156"/>
-      <c r="F12" s="156"/>
-      <c r="G12" s="156"/>
-      <c r="H12" s="156"/>
-      <c r="I12" s="156"/>
-      <c r="J12" s="156"/>
-      <c r="K12" s="156"/>
+      <c r="D12" s="160"/>
+      <c r="E12" s="160"/>
+      <c r="F12" s="160"/>
+      <c r="G12" s="160"/>
+      <c r="H12" s="160"/>
+      <c r="I12" s="160"/>
+      <c r="J12" s="160"/>
+      <c r="K12" s="160"/>
     </row>
     <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="51" t="s">
@@ -21423,14 +21509,14 @@
         <f>SUM(C5:C12)</f>
         <v>84.399999999999991</v>
       </c>
-      <c r="D13" s="156"/>
-      <c r="E13" s="156"/>
-      <c r="F13" s="156"/>
-      <c r="G13" s="156"/>
-      <c r="H13" s="156"/>
-      <c r="I13" s="156"/>
-      <c r="J13" s="156"/>
-      <c r="K13" s="156"/>
+      <c r="D13" s="160"/>
+      <c r="E13" s="160"/>
+      <c r="F13" s="160"/>
+      <c r="G13" s="160"/>
+      <c r="H13" s="160"/>
+      <c r="I13" s="160"/>
+      <c r="J13" s="160"/>
+      <c r="K13" s="160"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -21465,17 +21551,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="130" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -21483,18 +21569,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="130" t="s">
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="131"/>
+      <c r="I2" s="139"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -21506,18 +21592,18 @@
       <c r="A3" s="115">
         <v>1</v>
       </c>
-      <c r="B3" s="132" t="s">
+      <c r="B3" s="134" t="s">
         <v>645</v>
       </c>
-      <c r="C3" s="133"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="135" t="s">
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="140" t="s">
         <v>646</v>
       </c>
-      <c r="I3" s="136"/>
+      <c r="I3" s="141"/>
       <c r="J3" s="115" t="s">
         <v>20</v>
       </c>
@@ -21549,14 +21635,14 @@
       <c r="C5" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="D5" s="124"/>
-      <c r="E5" s="124"/>
-      <c r="F5" s="124"/>
-      <c r="G5" s="124"/>
-      <c r="H5" s="124"/>
-      <c r="I5" s="124"/>
-      <c r="J5" s="124"/>
-      <c r="K5" s="124"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="128"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="128"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
     </row>
     <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="116">
@@ -21568,14 +21654,14 @@
       <c r="C6" s="116">
         <v>1731.1</v>
       </c>
-      <c r="D6" s="124"/>
-      <c r="E6" s="124"/>
-      <c r="F6" s="124"/>
-      <c r="G6" s="124"/>
-      <c r="H6" s="124"/>
-      <c r="I6" s="124"/>
-      <c r="J6" s="124"/>
-      <c r="K6" s="124"/>
+      <c r="D6" s="128"/>
+      <c r="E6" s="128"/>
+      <c r="F6" s="128"/>
+      <c r="G6" s="128"/>
+      <c r="H6" s="128"/>
+      <c r="I6" s="128"/>
+      <c r="J6" s="128"/>
+      <c r="K6" s="128"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="117">
@@ -21587,14 +21673,14 @@
       <c r="C7" s="117">
         <v>4073.1</v>
       </c>
-      <c r="D7" s="124"/>
-      <c r="E7" s="124"/>
-      <c r="F7" s="124"/>
-      <c r="G7" s="124"/>
-      <c r="H7" s="124"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="124"/>
-      <c r="K7" s="124"/>
+      <c r="D7" s="128"/>
+      <c r="E7" s="128"/>
+      <c r="F7" s="128"/>
+      <c r="G7" s="128"/>
+      <c r="H7" s="128"/>
+      <c r="I7" s="128"/>
+      <c r="J7" s="128"/>
+      <c r="K7" s="128"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="116">
@@ -21606,32 +21692,32 @@
       <c r="C8" s="116">
         <v>3504.6</v>
       </c>
-      <c r="D8" s="124"/>
-      <c r="E8" s="124"/>
-      <c r="F8" s="124"/>
-      <c r="G8" s="124"/>
-      <c r="H8" s="124"/>
-      <c r="I8" s="124"/>
-      <c r="J8" s="124"/>
-      <c r="K8" s="124"/>
+      <c r="D8" s="128"/>
+      <c r="E8" s="128"/>
+      <c r="F8" s="128"/>
+      <c r="G8" s="128"/>
+      <c r="H8" s="128"/>
+      <c r="I8" s="128"/>
+      <c r="J8" s="128"/>
+      <c r="K8" s="128"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="125" t="s">
+      <c r="A9" s="129" t="s">
         <v>630</v>
       </c>
-      <c r="B9" s="125"/>
+      <c r="B9" s="129"/>
       <c r="C9" s="118">
         <f>SUM(C6:C8)</f>
         <v>9308.7999999999993</v>
       </c>
-      <c r="D9" s="124"/>
-      <c r="E9" s="124"/>
-      <c r="F9" s="124"/>
-      <c r="G9" s="124"/>
-      <c r="H9" s="124"/>
-      <c r="I9" s="124"/>
-      <c r="J9" s="124"/>
-      <c r="K9" s="124"/>
+      <c r="D9" s="128"/>
+      <c r="E9" s="128"/>
+      <c r="F9" s="128"/>
+      <c r="G9" s="128"/>
+      <c r="H9" s="128"/>
+      <c r="I9" s="128"/>
+      <c r="J9" s="128"/>
+      <c r="K9" s="128"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -21668,25 +21754,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="154" t="s">
         <v>688</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
+      <c r="B1" s="154"/>
+      <c r="C1" s="154"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="154"/>
+      <c r="F1" s="154"/>
+      <c r="G1" s="154"/>
     </row>
     <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="114" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="151" t="s">
+      <c r="B2" s="155" t="s">
         <v>687</v>
       </c>
-      <c r="C2" s="152"/>
-      <c r="D2" s="153"/>
+      <c r="C2" s="156"/>
+      <c r="D2" s="157"/>
       <c r="E2" s="113" t="s">
         <v>631</v>
       </c>
@@ -21701,11 +21787,11 @@
       <c r="A3" s="108">
         <v>1</v>
       </c>
-      <c r="B3" s="138" t="s">
+      <c r="B3" s="142" t="s">
         <v>693</v>
       </c>
-      <c r="C3" s="139"/>
-      <c r="D3" s="140"/>
+      <c r="C3" s="143"/>
+      <c r="D3" s="144"/>
       <c r="E3" s="111" t="s">
         <v>692</v>
       </c>
@@ -21721,11 +21807,11 @@
       <c r="A4" s="108">
         <v>2</v>
       </c>
-      <c r="B4" s="138" t="s">
+      <c r="B4" s="142" t="s">
         <v>690</v>
       </c>
-      <c r="C4" s="139"/>
-      <c r="D4" s="140"/>
+      <c r="C4" s="143"/>
+      <c r="D4" s="144"/>
       <c r="E4" s="111" t="s">
         <v>691</v>
       </c>
@@ -21741,11 +21827,11 @@
       <c r="A5" s="108">
         <v>3</v>
       </c>
-      <c r="B5" s="138" t="s">
+      <c r="B5" s="142" t="s">
         <v>689</v>
       </c>
-      <c r="C5" s="139"/>
-      <c r="D5" s="140"/>
+      <c r="C5" s="143"/>
+      <c r="D5" s="144"/>
       <c r="E5" s="111" t="s">
         <v>695</v>
       </c>
@@ -21761,11 +21847,11 @@
       <c r="A6" s="108">
         <v>4</v>
       </c>
-      <c r="B6" s="138" t="s">
+      <c r="B6" s="142" t="s">
         <v>685</v>
       </c>
-      <c r="C6" s="139"/>
-      <c r="D6" s="140"/>
+      <c r="C6" s="143"/>
+      <c r="D6" s="144"/>
       <c r="E6" s="111" t="s">
         <v>694</v>
       </c>
@@ -21778,24 +21864,24 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="141"/>
-      <c r="B7" s="141"/>
-      <c r="C7" s="141"/>
-      <c r="D7" s="141"/>
-      <c r="E7" s="141"/>
-      <c r="F7" s="141"/>
-      <c r="G7" s="141"/>
+      <c r="A7" s="145"/>
+      <c r="B7" s="145"/>
+      <c r="C7" s="145"/>
+      <c r="D7" s="145"/>
+      <c r="E7" s="145"/>
+      <c r="F7" s="145"/>
+      <c r="G7" s="145"/>
     </row>
     <row r="8" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="145" t="s">
+      <c r="A8" s="149" t="s">
         <v>684</v>
       </c>
-      <c r="B8" s="146"/>
-      <c r="C8" s="146"/>
-      <c r="D8" s="147"/>
-      <c r="E8" s="149"/>
-      <c r="F8" s="149"/>
-      <c r="G8" s="149"/>
+      <c r="B8" s="150"/>
+      <c r="C8" s="150"/>
+      <c r="D8" s="151"/>
+      <c r="E8" s="153"/>
+      <c r="F8" s="153"/>
+      <c r="G8" s="153"/>
     </row>
     <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="108" t="s">
@@ -21810,9 +21896,9 @@
       <c r="D9" s="108" t="s">
         <v>680</v>
       </c>
-      <c r="E9" s="149"/>
-      <c r="F9" s="149"/>
-      <c r="G9" s="149"/>
+      <c r="E9" s="153"/>
+      <c r="F9" s="153"/>
+      <c r="G9" s="153"/>
     </row>
     <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="108">
@@ -21827,9 +21913,9 @@
       <c r="D10" s="107">
         <v>14.8</v>
       </c>
-      <c r="E10" s="149"/>
-      <c r="F10" s="149"/>
-      <c r="G10" s="149"/>
+      <c r="E10" s="153"/>
+      <c r="F10" s="153"/>
+      <c r="G10" s="153"/>
     </row>
     <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="108">
@@ -21845,9 +21931,9 @@
         <f>2.25+5.7</f>
         <v>7.95</v>
       </c>
-      <c r="E11" s="149"/>
-      <c r="F11" s="149"/>
-      <c r="G11" s="149"/>
+      <c r="E11" s="153"/>
+      <c r="F11" s="153"/>
+      <c r="G11" s="153"/>
     </row>
     <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="108">
@@ -21862,9 +21948,9 @@
       <c r="D12" s="107">
         <v>35.200000000000003</v>
       </c>
-      <c r="E12" s="149"/>
-      <c r="F12" s="149"/>
-      <c r="G12" s="149"/>
+      <c r="E12" s="153"/>
+      <c r="F12" s="153"/>
+      <c r="G12" s="153"/>
     </row>
     <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="119">
@@ -21879,9 +21965,9 @@
       <c r="D13" s="107">
         <v>19.8</v>
       </c>
-      <c r="E13" s="149"/>
-      <c r="F13" s="149"/>
-      <c r="G13" s="149"/>
+      <c r="E13" s="153"/>
+      <c r="F13" s="153"/>
+      <c r="G13" s="153"/>
     </row>
     <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="108">
@@ -21897,9 +21983,9 @@
       <c r="D14" s="107">
         <v>24.1</v>
       </c>
-      <c r="E14" s="149"/>
-      <c r="F14" s="149"/>
-      <c r="G14" s="149"/>
+      <c r="E14" s="153"/>
+      <c r="F14" s="153"/>
+      <c r="G14" s="153"/>
     </row>
     <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="108">
@@ -21915,15 +22001,15 @@
       <c r="D15" s="107">
         <v>20.3</v>
       </c>
-      <c r="E15" s="149"/>
-      <c r="F15" s="149"/>
-      <c r="G15" s="149"/>
+      <c r="E15" s="153"/>
+      <c r="F15" s="153"/>
+      <c r="G15" s="153"/>
     </row>
     <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="142" t="s">
+      <c r="A16" s="146" t="s">
         <v>630</v>
       </c>
-      <c r="B16" s="143"/>
+      <c r="B16" s="147"/>
       <c r="C16" s="109">
         <f>SUM(C10:C15)</f>
         <v>120.35000000000001</v>
@@ -21932,29 +22018,29 @@
         <f>SUM(D10:D15)</f>
         <v>122.14999999999999</v>
       </c>
-      <c r="E16" s="149"/>
-      <c r="F16" s="149"/>
-      <c r="G16" s="149"/>
+      <c r="E16" s="153"/>
+      <c r="F16" s="153"/>
+      <c r="G16" s="153"/>
     </row>
     <row r="17" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="148"/>
-      <c r="B17" s="148"/>
-      <c r="C17" s="148"/>
-      <c r="D17" s="148"/>
-      <c r="E17" s="149"/>
-      <c r="F17" s="149"/>
-      <c r="G17" s="149"/>
+      <c r="A17" s="152"/>
+      <c r="B17" s="152"/>
+      <c r="C17" s="152"/>
+      <c r="D17" s="152"/>
+      <c r="E17" s="153"/>
+      <c r="F17" s="153"/>
+      <c r="G17" s="153"/>
     </row>
     <row r="18" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="144" t="s">
+      <c r="A18" s="148" t="s">
         <v>678</v>
       </c>
-      <c r="B18" s="144"/>
-      <c r="C18" s="144"/>
-      <c r="D18" s="144"/>
-      <c r="E18" s="149"/>
-      <c r="F18" s="149"/>
-      <c r="G18" s="149"/>
+      <c r="B18" s="148"/>
+      <c r="C18" s="148"/>
+      <c r="D18" s="148"/>
+      <c r="E18" s="153"/>
+      <c r="F18" s="153"/>
+      <c r="G18" s="153"/>
     </row>
     <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="108">
@@ -21969,9 +22055,9 @@
       <c r="D19" s="107">
         <v>9.9</v>
       </c>
-      <c r="E19" s="149"/>
-      <c r="F19" s="149"/>
-      <c r="G19" s="149"/>
+      <c r="E19" s="153"/>
+      <c r="F19" s="153"/>
+      <c r="G19" s="153"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -22007,23 +22093,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="154" t="s">
+      <c r="A1" s="158" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
     </row>
     <row r="2" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="129"/>
+      <c r="C2" s="133"/>
       <c r="D2" s="99" t="s">
         <v>631</v>
       </c>
@@ -22038,10 +22124,10 @@
       <c r="A3" s="98">
         <v>1</v>
       </c>
-      <c r="B3" s="132" t="s">
+      <c r="B3" s="134" t="s">
         <v>676</v>
       </c>
-      <c r="C3" s="134"/>
+      <c r="C3" s="136"/>
       <c r="D3" s="100" t="s">
         <v>675</v>
       </c>
@@ -22068,10 +22154,10 @@
       <c r="B5" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="C5" s="156"/>
-      <c r="D5" s="156"/>
-      <c r="E5" s="156"/>
-      <c r="F5" s="156"/>
+      <c r="C5" s="160"/>
+      <c r="D5" s="160"/>
+      <c r="E5" s="160"/>
+      <c r="F5" s="160"/>
     </row>
     <row r="6" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="64">
@@ -22081,10 +22167,10 @@
         <f>1581.9+140.9</f>
         <v>1722.8000000000002</v>
       </c>
-      <c r="C6" s="156"/>
-      <c r="D6" s="156"/>
-      <c r="E6" s="156"/>
-      <c r="F6" s="156"/>
+      <c r="C6" s="160"/>
+      <c r="D6" s="160"/>
+      <c r="E6" s="160"/>
+      <c r="F6" s="160"/>
     </row>
     <row r="7" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="54">
@@ -22093,10 +22179,10 @@
       <c r="B7" s="104">
         <v>4179.3</v>
       </c>
-      <c r="C7" s="156"/>
-      <c r="D7" s="156"/>
-      <c r="E7" s="156"/>
-      <c r="F7" s="156"/>
+      <c r="C7" s="160"/>
+      <c r="D7" s="160"/>
+      <c r="E7" s="160"/>
+      <c r="F7" s="160"/>
     </row>
     <row r="8" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="64">
@@ -22105,10 +22191,10 @@
       <c r="B8" s="103">
         <v>3580.3</v>
       </c>
-      <c r="C8" s="156"/>
-      <c r="D8" s="156"/>
-      <c r="E8" s="156"/>
-      <c r="F8" s="156"/>
+      <c r="C8" s="160"/>
+      <c r="D8" s="160"/>
+      <c r="E8" s="160"/>
+      <c r="F8" s="160"/>
     </row>
     <row r="9" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="102" t="s">
@@ -22118,10 +22204,10 @@
         <f>SUM(B6:B8)</f>
         <v>9482.4000000000015</v>
       </c>
-      <c r="C9" s="156"/>
-      <c r="D9" s="156"/>
-      <c r="E9" s="156"/>
-      <c r="F9" s="156"/>
+      <c r="C9" s="160"/>
+      <c r="D9" s="160"/>
+      <c r="E9" s="160"/>
+      <c r="F9" s="160"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -22155,17 +22241,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="130" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -22173,18 +22259,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="130" t="s">
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="131"/>
+      <c r="I2" s="139"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -22196,18 +22282,18 @@
       <c r="A3" s="97">
         <v>1</v>
       </c>
-      <c r="B3" s="132" t="s">
+      <c r="B3" s="134" t="s">
         <v>645</v>
       </c>
-      <c r="C3" s="133"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="135" t="s">
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="140" t="s">
         <v>646</v>
       </c>
-      <c r="I3" s="136"/>
+      <c r="I3" s="141"/>
       <c r="J3" s="97" t="s">
         <v>20</v>
       </c>
@@ -22239,7 +22325,7 @@
       <c r="C5" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="D5" s="156"/>
+      <c r="D5" s="160"/>
       <c r="E5" s="69" t="s">
         <v>647</v>
       </c>
@@ -22249,7 +22335,7 @@
       <c r="G5" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="H5" s="156"/>
+      <c r="H5" s="160"/>
       <c r="I5" s="69" t="s">
         <v>647</v>
       </c>
@@ -22270,7 +22356,7 @@
       <c r="C6" s="64">
         <v>25.1</v>
       </c>
-      <c r="D6" s="156"/>
+      <c r="D6" s="160"/>
       <c r="E6" s="64">
         <v>27</v>
       </c>
@@ -22280,7 +22366,7 @@
       <c r="G6" s="64">
         <v>13.4</v>
       </c>
-      <c r="H6" s="156"/>
+      <c r="H6" s="160"/>
       <c r="I6" s="64">
         <v>57</v>
       </c>
@@ -22301,7 +22387,7 @@
       <c r="C7" s="54">
         <v>12.5</v>
       </c>
-      <c r="D7" s="156"/>
+      <c r="D7" s="160"/>
       <c r="E7" s="54">
         <v>28</v>
       </c>
@@ -22311,7 +22397,7 @@
       <c r="G7" s="54">
         <v>10.26</v>
       </c>
-      <c r="H7" s="156"/>
+      <c r="H7" s="160"/>
       <c r="I7" s="54">
         <v>58</v>
       </c>
@@ -22332,7 +22418,7 @@
       <c r="C8" s="64">
         <v>5.4</v>
       </c>
-      <c r="D8" s="156"/>
+      <c r="D8" s="160"/>
       <c r="E8" s="64">
         <v>29</v>
       </c>
@@ -22342,7 +22428,7 @@
       <c r="G8" s="64">
         <v>23.4</v>
       </c>
-      <c r="H8" s="156"/>
+      <c r="H8" s="160"/>
       <c r="I8" s="64">
         <v>59</v>
       </c>
@@ -22363,7 +22449,7 @@
       <c r="C9" s="54">
         <v>21</v>
       </c>
-      <c r="D9" s="156"/>
+      <c r="D9" s="160"/>
       <c r="E9" s="54">
         <v>30</v>
       </c>
@@ -22373,7 +22459,7 @@
       <c r="G9" s="54">
         <v>4.67</v>
       </c>
-      <c r="H9" s="156"/>
+      <c r="H9" s="160"/>
       <c r="I9" s="54">
         <v>60</v>
       </c>
@@ -22394,7 +22480,7 @@
       <c r="C10" s="64">
         <v>5.8</v>
       </c>
-      <c r="D10" s="156"/>
+      <c r="D10" s="160"/>
       <c r="E10" s="64">
         <v>31</v>
       </c>
@@ -22404,7 +22490,7 @@
       <c r="G10" s="64">
         <v>19.239999999999998</v>
       </c>
-      <c r="H10" s="156"/>
+      <c r="H10" s="160"/>
       <c r="I10" s="64">
         <v>61</v>
       </c>
@@ -22425,7 +22511,7 @@
       <c r="C11" s="54">
         <v>32.200000000000003</v>
       </c>
-      <c r="D11" s="156"/>
+      <c r="D11" s="160"/>
       <c r="E11" s="54">
         <v>32</v>
       </c>
@@ -22435,7 +22521,7 @@
       <c r="G11" s="54">
         <v>19.829999999999998</v>
       </c>
-      <c r="H11" s="156"/>
+      <c r="H11" s="160"/>
       <c r="I11" s="54">
         <v>62</v>
       </c>
@@ -22456,7 +22542,7 @@
       <c r="C12" s="64">
         <v>12.2</v>
       </c>
-      <c r="D12" s="156"/>
+      <c r="D12" s="160"/>
       <c r="E12" s="64">
         <v>33</v>
       </c>
@@ -22466,7 +22552,7 @@
       <c r="G12" s="64">
         <v>10.25</v>
       </c>
-      <c r="H12" s="156"/>
+      <c r="H12" s="160"/>
       <c r="I12" s="64">
         <v>63</v>
       </c>
@@ -22487,7 +22573,7 @@
       <c r="C13" s="54">
         <v>7.5</v>
       </c>
-      <c r="D13" s="156"/>
+      <c r="D13" s="160"/>
       <c r="E13" s="54">
         <v>34</v>
       </c>
@@ -22497,7 +22583,7 @@
       <c r="G13" s="54">
         <v>5.44</v>
       </c>
-      <c r="H13" s="156"/>
+      <c r="H13" s="160"/>
       <c r="I13" s="54">
         <v>64</v>
       </c>
@@ -22518,7 +22604,7 @@
       <c r="C14" s="64">
         <v>8.1999999999999993</v>
       </c>
-      <c r="D14" s="156"/>
+      <c r="D14" s="160"/>
       <c r="E14" s="64">
         <v>35</v>
       </c>
@@ -22528,7 +22614,7 @@
       <c r="G14" s="64">
         <v>4.55</v>
       </c>
-      <c r="H14" s="156"/>
+      <c r="H14" s="160"/>
       <c r="I14" s="64">
         <v>65</v>
       </c>
@@ -22549,7 +22635,7 @@
       <c r="C15" s="54">
         <v>8.9</v>
       </c>
-      <c r="D15" s="156"/>
+      <c r="D15" s="160"/>
       <c r="E15" s="54">
         <v>36</v>
       </c>
@@ -22559,7 +22645,7 @@
       <c r="G15" s="54">
         <v>15.17</v>
       </c>
-      <c r="H15" s="156"/>
+      <c r="H15" s="160"/>
       <c r="I15" s="54">
         <v>66</v>
       </c>
@@ -22580,7 +22666,7 @@
       <c r="C16" s="64">
         <v>15.2</v>
       </c>
-      <c r="D16" s="156"/>
+      <c r="D16" s="160"/>
       <c r="E16" s="64">
         <v>37</v>
       </c>
@@ -22590,7 +22676,7 @@
       <c r="G16" s="64">
         <v>10.79</v>
       </c>
-      <c r="H16" s="156"/>
+      <c r="H16" s="160"/>
       <c r="I16" s="64">
         <v>67</v>
       </c>
@@ -22611,7 +22697,7 @@
       <c r="C17" s="54">
         <v>14</v>
       </c>
-      <c r="D17" s="156"/>
+      <c r="D17" s="160"/>
       <c r="E17" s="54">
         <v>38</v>
       </c>
@@ -22621,7 +22707,7 @@
       <c r="G17" s="54">
         <v>10.34</v>
       </c>
-      <c r="H17" s="156"/>
+      <c r="H17" s="160"/>
       <c r="I17" s="54">
         <v>68</v>
       </c>
@@ -22642,7 +22728,7 @@
       <c r="C18" s="64">
         <v>12.1</v>
       </c>
-      <c r="D18" s="156"/>
+      <c r="D18" s="160"/>
       <c r="E18" s="64">
         <v>39</v>
       </c>
@@ -22652,7 +22738,7 @@
       <c r="G18" s="64">
         <v>7.99</v>
       </c>
-      <c r="H18" s="156"/>
+      <c r="H18" s="160"/>
       <c r="I18" s="64">
         <v>69</v>
       </c>
@@ -22673,7 +22759,7 @@
       <c r="C19" s="54">
         <v>15.28</v>
       </c>
-      <c r="D19" s="156"/>
+      <c r="D19" s="160"/>
       <c r="E19" s="54">
         <v>40</v>
       </c>
@@ -22683,7 +22769,7 @@
       <c r="G19" s="54">
         <v>7.6</v>
       </c>
-      <c r="H19" s="156"/>
+      <c r="H19" s="160"/>
       <c r="I19" s="54">
         <v>70</v>
       </c>
@@ -22704,7 +22790,7 @@
       <c r="C20" s="64">
         <v>8.1999999999999993</v>
       </c>
-      <c r="D20" s="156"/>
+      <c r="D20" s="160"/>
       <c r="E20" s="64">
         <v>41</v>
       </c>
@@ -22714,7 +22800,7 @@
       <c r="G20" s="64">
         <v>10.37</v>
       </c>
-      <c r="H20" s="156"/>
+      <c r="H20" s="160"/>
       <c r="I20" s="64">
         <v>71</v>
       </c>
@@ -22735,7 +22821,7 @@
       <c r="C21" s="54">
         <v>7.7</v>
       </c>
-      <c r="D21" s="156"/>
+      <c r="D21" s="160"/>
       <c r="E21" s="54">
         <v>42</v>
       </c>
@@ -22745,7 +22831,7 @@
       <c r="G21" s="54">
         <v>16.13</v>
       </c>
-      <c r="H21" s="156"/>
+      <c r="H21" s="160"/>
       <c r="I21" s="54">
         <v>72</v>
       </c>
@@ -22766,7 +22852,7 @@
       <c r="C22" s="64">
         <v>14.6</v>
       </c>
-      <c r="D22" s="156"/>
+      <c r="D22" s="160"/>
       <c r="E22" s="64">
         <v>43</v>
       </c>
@@ -22776,7 +22862,7 @@
       <c r="G22" s="64">
         <v>22.18</v>
       </c>
-      <c r="H22" s="156"/>
+      <c r="H22" s="160"/>
       <c r="I22" s="64">
         <v>73</v>
       </c>
@@ -22797,7 +22883,7 @@
       <c r="C23" s="54">
         <v>12.7</v>
       </c>
-      <c r="D23" s="156"/>
+      <c r="D23" s="160"/>
       <c r="E23" s="54">
         <v>44</v>
       </c>
@@ -22807,7 +22893,7 @@
       <c r="G23" s="54">
         <v>4.37</v>
       </c>
-      <c r="H23" s="156"/>
+      <c r="H23" s="160"/>
       <c r="I23" s="54">
         <v>74</v>
       </c>
@@ -22828,7 +22914,7 @@
       <c r="C24" s="64">
         <v>37</v>
       </c>
-      <c r="D24" s="156"/>
+      <c r="D24" s="160"/>
       <c r="E24" s="64">
         <v>45</v>
       </c>
@@ -22838,7 +22924,7 @@
       <c r="G24" s="64">
         <v>5.64</v>
       </c>
-      <c r="H24" s="156"/>
+      <c r="H24" s="160"/>
       <c r="I24" s="64">
         <v>75</v>
       </c>
@@ -22859,7 +22945,7 @@
       <c r="C25" s="54">
         <v>7.4</v>
       </c>
-      <c r="D25" s="156"/>
+      <c r="D25" s="160"/>
       <c r="E25" s="54">
         <v>46</v>
       </c>
@@ -22869,7 +22955,7 @@
       <c r="G25" s="54">
         <v>25.37</v>
       </c>
-      <c r="H25" s="156"/>
+      <c r="H25" s="160"/>
       <c r="I25" s="54">
         <v>76</v>
       </c>
@@ -22890,7 +22976,7 @@
       <c r="C26" s="64">
         <v>117.2</v>
       </c>
-      <c r="D26" s="156"/>
+      <c r="D26" s="160"/>
       <c r="E26" s="64">
         <v>47</v>
       </c>
@@ -22900,7 +22986,7 @@
       <c r="G26" s="64">
         <v>5.64</v>
       </c>
-      <c r="H26" s="156"/>
+      <c r="H26" s="160"/>
       <c r="I26" s="64">
         <v>77</v>
       </c>
@@ -22921,7 +23007,7 @@
       <c r="C27" s="54">
         <v>20.7</v>
       </c>
-      <c r="D27" s="156"/>
+      <c r="D27" s="160"/>
       <c r="E27" s="54">
         <v>48</v>
       </c>
@@ -22931,7 +23017,7 @@
       <c r="G27" s="54">
         <v>25.37</v>
       </c>
-      <c r="H27" s="156"/>
+      <c r="H27" s="160"/>
       <c r="I27" s="54">
         <v>78</v>
       </c>
@@ -22952,7 +23038,7 @@
       <c r="C28" s="64">
         <v>37.4</v>
       </c>
-      <c r="D28" s="156"/>
+      <c r="D28" s="160"/>
       <c r="E28" s="64">
         <v>49</v>
       </c>
@@ -22962,7 +23048,7 @@
       <c r="G28" s="64">
         <v>9.07</v>
       </c>
-      <c r="H28" s="156"/>
+      <c r="H28" s="160"/>
       <c r="I28" s="64">
         <v>79</v>
       </c>
@@ -22983,7 +23069,7 @@
       <c r="C29" s="54">
         <v>13.1</v>
       </c>
-      <c r="D29" s="156"/>
+      <c r="D29" s="160"/>
       <c r="E29" s="54">
         <v>50</v>
       </c>
@@ -22993,7 +23079,7 @@
       <c r="G29" s="54">
         <v>16.559999999999999</v>
       </c>
-      <c r="H29" s="156"/>
+      <c r="H29" s="160"/>
       <c r="J29" s="51" t="s">
         <v>630</v>
       </c>
@@ -23012,7 +23098,7 @@
       <c r="C30" s="64">
         <v>16.899999999999999</v>
       </c>
-      <c r="D30" s="156"/>
+      <c r="D30" s="160"/>
       <c r="E30" s="64">
         <v>51</v>
       </c>
@@ -23022,10 +23108,10 @@
       <c r="G30" s="64">
         <v>8.1199999999999992</v>
       </c>
-      <c r="H30" s="156"/>
-      <c r="I30" s="156"/>
-      <c r="J30" s="156"/>
-      <c r="K30" s="156"/>
+      <c r="H30" s="160"/>
+      <c r="I30" s="160"/>
+      <c r="J30" s="160"/>
+      <c r="K30" s="160"/>
     </row>
     <row r="31" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="54">
@@ -23037,7 +23123,7 @@
       <c r="C31" s="54">
         <v>104</v>
       </c>
-      <c r="D31" s="156"/>
+      <c r="D31" s="160"/>
       <c r="E31" s="54">
         <v>52</v>
       </c>
@@ -23047,10 +23133,10 @@
       <c r="G31" s="54">
         <v>8.89</v>
       </c>
-      <c r="H31" s="156"/>
-      <c r="I31" s="156"/>
-      <c r="J31" s="156"/>
-      <c r="K31" s="156"/>
+      <c r="H31" s="160"/>
+      <c r="I31" s="160"/>
+      <c r="J31" s="160"/>
+      <c r="K31" s="160"/>
     </row>
     <row r="32" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="51" t="s">
@@ -23060,7 +23146,7 @@
         <f>SUM(C6:C31)</f>
         <v>592.27999999999986</v>
       </c>
-      <c r="D32" s="156"/>
+      <c r="D32" s="160"/>
       <c r="E32" s="64">
         <v>53</v>
       </c>
@@ -23070,16 +23156,16 @@
       <c r="G32" s="64">
         <v>9.69</v>
       </c>
-      <c r="H32" s="156"/>
-      <c r="I32" s="156"/>
-      <c r="J32" s="156"/>
-      <c r="K32" s="156"/>
+      <c r="H32" s="160"/>
+      <c r="I32" s="160"/>
+      <c r="J32" s="160"/>
+      <c r="K32" s="160"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="124"/>
-      <c r="B33" s="124"/>
-      <c r="C33" s="124"/>
-      <c r="D33" s="156"/>
+      <c r="A33" s="128"/>
+      <c r="B33" s="128"/>
+      <c r="C33" s="128"/>
+      <c r="D33" s="160"/>
       <c r="E33" s="54">
         <v>54</v>
       </c>
@@ -23089,16 +23175,16 @@
       <c r="G33" s="54">
         <v>4.1900000000000004</v>
       </c>
-      <c r="H33" s="156"/>
-      <c r="I33" s="156"/>
-      <c r="J33" s="156"/>
-      <c r="K33" s="156"/>
+      <c r="H33" s="160"/>
+      <c r="I33" s="160"/>
+      <c r="J33" s="160"/>
+      <c r="K33" s="160"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A34" s="124"/>
-      <c r="B34" s="124"/>
-      <c r="C34" s="124"/>
-      <c r="D34" s="156"/>
+      <c r="A34" s="128"/>
+      <c r="B34" s="128"/>
+      <c r="C34" s="128"/>
+      <c r="D34" s="160"/>
       <c r="E34" s="64">
         <v>55</v>
       </c>
@@ -23108,16 +23194,16 @@
       <c r="G34" s="64">
         <v>19.78</v>
       </c>
-      <c r="H34" s="156"/>
-      <c r="I34" s="156"/>
-      <c r="J34" s="156"/>
-      <c r="K34" s="156"/>
+      <c r="H34" s="160"/>
+      <c r="I34" s="160"/>
+      <c r="J34" s="160"/>
+      <c r="K34" s="160"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="124"/>
-      <c r="B35" s="124"/>
-      <c r="C35" s="124"/>
-      <c r="D35" s="156"/>
+      <c r="A35" s="128"/>
+      <c r="B35" s="128"/>
+      <c r="C35" s="128"/>
+      <c r="D35" s="160"/>
       <c r="E35" s="54">
         <v>56</v>
       </c>
@@ -23127,16 +23213,16 @@
       <c r="G35" s="54">
         <v>8.25</v>
       </c>
-      <c r="H35" s="156"/>
-      <c r="I35" s="156"/>
-      <c r="J35" s="156"/>
-      <c r="K35" s="156"/>
+      <c r="H35" s="160"/>
+      <c r="I35" s="160"/>
+      <c r="J35" s="160"/>
+      <c r="K35" s="160"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" s="124"/>
-      <c r="B36" s="124"/>
-      <c r="C36" s="124"/>
-      <c r="D36" s="156"/>
+      <c r="A36" s="128"/>
+      <c r="B36" s="128"/>
+      <c r="C36" s="128"/>
+      <c r="D36" s="160"/>
       <c r="F36" s="51" t="s">
         <v>630</v>
       </c>
@@ -23144,10 +23230,10 @@
         <f>SUM(G6:G35)</f>
         <v>362.54999999999995</v>
       </c>
-      <c r="H36" s="156"/>
-      <c r="I36" s="156"/>
-      <c r="J36" s="156"/>
-      <c r="K36" s="156"/>
+      <c r="H36" s="160"/>
+      <c r="I36" s="160"/>
+      <c r="J36" s="160"/>
+      <c r="K36" s="160"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -23183,14 +23269,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="130" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
       <c r="G1" s="70"/>
       <c r="H1" s="70"/>
     </row>
@@ -23198,15 +23284,15 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="158" t="s">
+      <c r="B2" s="162" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="160" t="s">
+      <c r="C2" s="162"/>
+      <c r="D2" s="162"/>
+      <c r="E2" s="164" t="s">
         <v>631</v>
       </c>
-      <c r="F2" s="160"/>
+      <c r="F2" s="164"/>
       <c r="G2" s="67" t="s">
         <v>5</v>
       </c>
@@ -23218,15 +23304,15 @@
       <c r="A3" s="79">
         <v>1</v>
       </c>
-      <c r="B3" s="159" t="s">
+      <c r="B3" s="163" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="161" t="s">
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="165" t="s">
         <v>192</v>
       </c>
-      <c r="F3" s="161"/>
+      <c r="F3" s="165"/>
       <c r="G3" s="79" t="s">
         <v>20</v>
       </c>
@@ -23236,14 +23322,14 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="156"/>
-      <c r="B4" s="156"/>
-      <c r="C4" s="156"/>
-      <c r="D4" s="156"/>
-      <c r="E4" s="156"/>
-      <c r="F4" s="156"/>
-      <c r="G4" s="156"/>
-      <c r="H4" s="156"/>
+      <c r="A4" s="160"/>
+      <c r="B4" s="160"/>
+      <c r="C4" s="160"/>
+      <c r="D4" s="160"/>
+      <c r="E4" s="160"/>
+      <c r="F4" s="160"/>
+      <c r="G4" s="160"/>
+      <c r="H4" s="160"/>
     </row>
     <row r="5" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="69" t="s">
@@ -23261,9 +23347,9 @@
       <c r="E5" s="69" t="s">
         <v>641</v>
       </c>
-      <c r="F5" s="124"/>
-      <c r="G5" s="124"/>
-      <c r="H5" s="124"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="128"/>
+      <c r="H5" s="128"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="84" t="s">
@@ -23282,9 +23368,9 @@
         <f>C6*D6</f>
         <v>6.9375</v>
       </c>
-      <c r="F6" s="124"/>
-      <c r="G6" s="124"/>
-      <c r="H6" s="124"/>
+      <c r="F6" s="128"/>
+      <c r="G6" s="128"/>
+      <c r="H6" s="128"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="83" t="s">
@@ -23303,9 +23389,9 @@
         <f>C7*D7</f>
         <v>9.84</v>
       </c>
-      <c r="F7" s="124"/>
-      <c r="G7" s="124"/>
-      <c r="H7" s="124"/>
+      <c r="F7" s="128"/>
+      <c r="G7" s="128"/>
+      <c r="H7" s="128"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="84" t="s">
@@ -23324,9 +23410,9 @@
         <f t="shared" ref="E8:E11" si="0">C8*D8</f>
         <v>1.425</v>
       </c>
-      <c r="F8" s="124"/>
-      <c r="G8" s="124"/>
-      <c r="H8" s="124"/>
+      <c r="F8" s="128"/>
+      <c r="G8" s="128"/>
+      <c r="H8" s="128"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="83" t="s">
@@ -23345,9 +23431,9 @@
         <f t="shared" si="0"/>
         <v>1.395</v>
       </c>
-      <c r="F9" s="124"/>
-      <c r="G9" s="124"/>
-      <c r="H9" s="124"/>
+      <c r="F9" s="128"/>
+      <c r="G9" s="128"/>
+      <c r="H9" s="128"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="84" t="s">
@@ -23366,9 +23452,9 @@
         <f t="shared" si="0"/>
         <v>1.5450000000000002</v>
       </c>
-      <c r="F10" s="124"/>
-      <c r="G10" s="124"/>
-      <c r="H10" s="124"/>
+      <c r="F10" s="128"/>
+      <c r="G10" s="128"/>
+      <c r="H10" s="128"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="83" t="s">
@@ -23387,9 +23473,9 @@
         <f t="shared" si="0"/>
         <v>1.38</v>
       </c>
-      <c r="F11" s="124"/>
-      <c r="G11" s="124"/>
-      <c r="H11" s="124"/>
+      <c r="F11" s="128"/>
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="84" t="s">
@@ -23408,14 +23494,14 @@
         <f t="shared" ref="E12" si="1">C12*D12</f>
         <v>1.38</v>
       </c>
-      <c r="F12" s="124"/>
-      <c r="G12" s="124"/>
-      <c r="H12" s="124"/>
+      <c r="F12" s="128"/>
+      <c r="G12" s="128"/>
+      <c r="H12" s="128"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="157"/>
-      <c r="B13" s="157"/>
-      <c r="C13" s="157"/>
+      <c r="A13" s="161"/>
+      <c r="B13" s="161"/>
+      <c r="C13" s="161"/>
       <c r="D13" t="s">
         <v>642</v>
       </c>
@@ -23423,9 +23509,9 @@
         <f>SUM(E6:E12)</f>
         <v>23.9025</v>
       </c>
-      <c r="F13" s="124"/>
-      <c r="G13" s="124"/>
-      <c r="H13" s="124"/>
+      <c r="F13" s="128"/>
+      <c r="G13" s="128"/>
+      <c r="H13" s="128"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -23461,17 +23547,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="130" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -23479,18 +23565,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="130" t="s">
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="131"/>
+      <c r="I2" s="139"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -23502,18 +23588,18 @@
       <c r="A3" s="89">
         <v>1</v>
       </c>
-      <c r="B3" s="132" t="s">
+      <c r="B3" s="134" t="s">
         <v>413</v>
       </c>
-      <c r="C3" s="133"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="162" t="s">
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="166" t="s">
         <v>644</v>
       </c>
-      <c r="I3" s="163"/>
+      <c r="I3" s="167"/>
       <c r="J3" s="89" t="s">
         <v>20</v>
       </c>
@@ -23526,18 +23612,18 @@
       <c r="A4" s="89">
         <v>2</v>
       </c>
-      <c r="B4" s="132" t="s">
+      <c r="B4" s="134" t="s">
         <v>387</v>
       </c>
-      <c r="C4" s="133"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="133"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="134"/>
-      <c r="H4" s="162" t="s">
+      <c r="C4" s="135"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="166" t="s">
         <v>643</v>
       </c>
-      <c r="I4" s="163"/>
+      <c r="I4" s="167"/>
       <c r="J4" s="89" t="s">
         <v>20</v>
       </c>
@@ -24036,17 +24122,17 @@
       <c r="K28" s="95"/>
     </row>
     <row r="31" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="126" t="s">
+      <c r="A31" s="130" t="s">
         <v>625</v>
       </c>
-      <c r="B31" s="126"/>
-      <c r="C31" s="126"/>
-      <c r="D31" s="126"/>
-      <c r="E31" s="126"/>
-      <c r="F31" s="126"/>
-      <c r="G31" s="126"/>
-      <c r="H31" s="126"/>
-      <c r="I31" s="126"/>
+      <c r="B31" s="130"/>
+      <c r="C31" s="130"/>
+      <c r="D31" s="130"/>
+      <c r="E31" s="130"/>
+      <c r="F31" s="130"/>
+      <c r="G31" s="130"/>
+      <c r="H31" s="130"/>
+      <c r="I31" s="130"/>
       <c r="J31" s="70"/>
       <c r="K31" s="70"/>
     </row>
@@ -24054,18 +24140,18 @@
       <c r="A32" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B32" s="127" t="s">
+      <c r="B32" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="128"/>
-      <c r="D32" s="128"/>
-      <c r="E32" s="128"/>
-      <c r="F32" s="128"/>
-      <c r="G32" s="129"/>
-      <c r="H32" s="130" t="s">
+      <c r="C32" s="132"/>
+      <c r="D32" s="132"/>
+      <c r="E32" s="132"/>
+      <c r="F32" s="132"/>
+      <c r="G32" s="133"/>
+      <c r="H32" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I32" s="131"/>
+      <c r="I32" s="139"/>
       <c r="J32" s="67" t="s">
         <v>5</v>
       </c>
@@ -24077,18 +24163,18 @@
       <c r="A33" s="89">
         <v>1</v>
       </c>
-      <c r="B33" s="132" t="s">
+      <c r="B33" s="134" t="s">
         <v>413</v>
       </c>
-      <c r="C33" s="133"/>
-      <c r="D33" s="133"/>
-      <c r="E33" s="133"/>
-      <c r="F33" s="133"/>
-      <c r="G33" s="134"/>
-      <c r="H33" s="162" t="s">
+      <c r="C33" s="135"/>
+      <c r="D33" s="135"/>
+      <c r="E33" s="135"/>
+      <c r="F33" s="135"/>
+      <c r="G33" s="136"/>
+      <c r="H33" s="166" t="s">
         <v>632</v>
       </c>
-      <c r="I33" s="163"/>
+      <c r="I33" s="167"/>
       <c r="J33" s="89" t="s">
         <v>20</v>
       </c>
@@ -24101,18 +24187,18 @@
       <c r="A34" s="89">
         <v>2</v>
       </c>
-      <c r="B34" s="132" t="s">
+      <c r="B34" s="134" t="s">
         <v>387</v>
       </c>
-      <c r="C34" s="133"/>
-      <c r="D34" s="133"/>
-      <c r="E34" s="133"/>
-      <c r="F34" s="133"/>
-      <c r="G34" s="134"/>
-      <c r="H34" s="162" t="s">
+      <c r="C34" s="135"/>
+      <c r="D34" s="135"/>
+      <c r="E34" s="135"/>
+      <c r="F34" s="135"/>
+      <c r="G34" s="136"/>
+      <c r="H34" s="166" t="s">
         <v>633</v>
       </c>
-      <c r="I34" s="163"/>
+      <c r="I34" s="167"/>
       <c r="J34" s="89" t="s">
         <v>20</v>
       </c>
@@ -24688,17 +24774,17 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="130" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -24706,18 +24792,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="130" t="s">
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="131"/>
+      <c r="I2" s="139"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -24729,18 +24815,18 @@
       <c r="A3" s="89">
         <v>1</v>
       </c>
-      <c r="B3" s="132" t="s">
+      <c r="B3" s="134" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="133"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="164" t="s">
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="168" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="163"/>
+      <c r="I3" s="167"/>
       <c r="J3" s="89" t="s">
         <v>20</v>
       </c>
@@ -25498,36 +25584,36 @@
       <c r="K41" s="81"/>
     </row>
     <row r="43" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="154" t="s">
+      <c r="A43" s="158" t="s">
         <v>625</v>
       </c>
-      <c r="B43" s="155"/>
-      <c r="C43" s="155"/>
-      <c r="D43" s="155"/>
-      <c r="E43" s="155"/>
-      <c r="F43" s="155"/>
-      <c r="G43" s="155"/>
-      <c r="H43" s="155"/>
-      <c r="I43" s="155"/>
-      <c r="J43" s="155"/>
-      <c r="K43" s="155"/>
+      <c r="B43" s="159"/>
+      <c r="C43" s="159"/>
+      <c r="D43" s="159"/>
+      <c r="E43" s="159"/>
+      <c r="F43" s="159"/>
+      <c r="G43" s="159"/>
+      <c r="H43" s="159"/>
+      <c r="I43" s="159"/>
+      <c r="J43" s="159"/>
+      <c r="K43" s="159"/>
     </row>
     <row r="44" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B44" s="127" t="s">
+      <c r="B44" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="C44" s="128"/>
-      <c r="D44" s="128"/>
-      <c r="E44" s="128"/>
-      <c r="F44" s="128"/>
-      <c r="G44" s="129"/>
-      <c r="H44" s="130" t="s">
+      <c r="C44" s="132"/>
+      <c r="D44" s="132"/>
+      <c r="E44" s="132"/>
+      <c r="F44" s="132"/>
+      <c r="G44" s="133"/>
+      <c r="H44" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I44" s="131"/>
+      <c r="I44" s="139"/>
       <c r="J44" s="67" t="s">
         <v>5</v>
       </c>
@@ -25539,18 +25625,18 @@
       <c r="A45" s="89">
         <v>1</v>
       </c>
-      <c r="B45" s="132" t="s">
+      <c r="B45" s="134" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="133"/>
-      <c r="D45" s="133"/>
-      <c r="E45" s="133"/>
-      <c r="F45" s="133"/>
-      <c r="G45" s="134"/>
-      <c r="H45" s="164" t="s">
+      <c r="C45" s="135"/>
+      <c r="D45" s="135"/>
+      <c r="E45" s="135"/>
+      <c r="F45" s="135"/>
+      <c r="G45" s="136"/>
+      <c r="H45" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="I45" s="163"/>
+      <c r="I45" s="167"/>
       <c r="J45" s="89" t="s">
         <v>20</v>
       </c>
